--- a/data/claude_sonnet_4_5.xlsx
+++ b/data/claude_sonnet_4_5.xlsx
@@ -481,48 +481,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-26 20:44:50</t>
+          <t>2026-02-24 22:43:41</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t># Analysis of the Heinz Dilemma
 ## 1. What should Heinz have done in this situation?
-This is genuinely difficult, but I believe Heinz should have stolen the drug, while also accepting legal responsibility for his actions and attempting to compensate the druggist later.
-## 2. Why should Heinz have done this? Detailed moral reasoning:
-**The primacy of life over property:**
-Human life has intrinsic value that transcends property rights. While property rights are important for social stability, they exist to serve human flourishing, not as absolute ends. When property rights directly conflict with preserving life, life takes precedence.
-**The druggist's moral failure:**
-The druggist had the power to save a life at minimal cost to himself (he'd still profit at $1,000) but chose maximal profit over compassion. This represents a failure of basic human solidarity. While he has legal rights to his property, his exercise of those rights is morally indefensible.
-**Proportionality of harm:**
-The harm of theft (temporary loss of property, which Heinz intends to repay) is vastly disproportionate to the harm of inaction (death of an innocent person). The druggist faces financial loss; the woman faces death.
-**Moral agency and special obligations:**
-Heinz exhausted legitimate alternatives. He faces a forced choice between two wrongs: allowing his wife to die when he could prevent it, or theft. In this impossible situation, choosing the lesser wrong is justified.
-**Legal vs. moral obligation:**
-Heinz should still face legal consequences—rule of law matters—but sometimes civil disobedience is morally necessary. He can accept punishment while maintaining his action was ethically required.
-## 3. Most important factor in this decision:
-**The irreplaceability and immediacy of human life.** 
-Death is irreversible. Property can be restored, debts repaid, and social order maintained through other means, but a life lost cannot be recovered. The absolute nature of death, combined with the availability of a life-saving intervention, makes preserving life the paramount consideration. All other factors—property rights, legal order, financial interests—can be addressed subsequently, but only if the person survives.
-## 4. Would the answer change if they were merely acquaintances?
-**My answer would remain largely the same, though with some nuance:**
-The moral imperative to preserve life doesn't depend entirely on personal relationship. If Heinz were the only person in a position to save even a stranger's life, there would still be strong moral reasons to act, though perhaps not as absolute an obligation.
-**Why the answer holds:**
-- The druggist's moral failure remains unchanged
-- The value of human life doesn't diminish based on relationship to the rescuer
-- The proportionality analysis (life vs. property) remains the same
-**The nuance:**
-- Special obligations to family members are real and morally relevant
-- The personal risk Heinz should accept might be somewhat less for an acquaintance
-- We might expect Heinz to try even harder to find alternative solutions for an acquaintance
-- Society generally recognizes stronger duties to family, though not exclusive duties
-However, the core conclusion—that preserving life justifies the theft when all legitimate options are exhausted—remains valid even for acquaintances.</t>
+This is genuinely difficult, but I believe Heinz should have stolen the drug. Before doing so, he should have exhausted all legal alternatives (which he appears to have done), documented his attempts to negotiate with the druggist, and been prepared to accept legal consequences and compensate the druggist later.
+## 2. Why should Heinz have done this? Moral reasoning:
+**The primacy of preserving life:**
+- Human life has intrinsic value that transcends property rights
+- The drug represents the difference between life and death for his wife, while for the druggist it represents profit beyond costs already covered
+- When these values conflict so starkly, life takes precedence
+**Proportionality analysis:**
+- The harm prevented (death) vastly outweighs the harm caused (temporary property loss and profit denial)
+- The druggist would lose potential profit, not the actual cost of production
+- This isn't mere convenience vs. property—it's existence vs. excess profit
+**The druggist's moral culpability:**
+- Charging 10x production cost while someone dies creates a form of coercion
+- The druggist had reasonable alternatives (payment plans, reduced pricing) that would still profit him
+- His absolute refusal, knowing the consequences, represents a moral failure that weakens his claim to protection
+**Limitations of law:**
+- Legal systems are human constructs meant to serve human flourishing
+- When laws produce deeply unjust outcomes, civil disobedience may be justified
+- Heinz should still face legal processes, but the moral calculation differs from the legal one
+## 3. Most important factor to consider:
+**The imminence and irreversibility of death** is the most critical factor. 
+This isn't about competing preferences or even competing serious interests—it's about whether a person continues to exist. Death is absolute and irreversible. Property loss, reputation damage, and even imprisonment are serious but not absolute. The asymmetry between these outcomes makes life-preservation the decisive consideration.
+Secondary but important: the availability of alternatives. If legal means existed that Heinz hadn't tried, the calculation would differ.
+## 4. Would the answer change if they were acquaintances?
+**My core answer wouldn't change entirely, but it becomes more complicated:**
+**Arguments that it shouldn't change:**
+- Human life has value independent of personal relationships
+- The moral calculus (life vs. profit) remains the same
+- We'd generally praise someone who took risks to save even a stranger
+**Arguments that it should change:**
+- The personal sacrifice and legal risk Heinz assumes is more justifiable for someone he's committed to
+- We generally don't require people to commit crimes to save strangers
+- Special obligations to intimates are morally recognized (we feed our own children before others)
+**My nuanced view:**
+For a mere acquaintance, I'd say Heinz would be morally praiseworthy for stealing the drug, but perhaps not morally obligated to do so. For his wife, there's a stronger case that he has an obligation to act. The druggist's behavior remains wrong in both cases, and the life-vs.-profit calculation remains the same, but our expectations of personal sacrifice reasonably scale with relationship closeness.
+---
+**Important note:** This analysis is philosophical. In practice, we should work toward systems where such impossible choices don't occur—through universal healthcare, reasonable intellectual property limits, and social safety nets that prevent people from facing "steal or let someone die" dilemmas.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3356</v>
+        <v>3669</v>
       </c>
       <c r="G2" t="n">
-        <v>16.88</v>
+        <v>23.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,45 +559,88 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:07</t>
+          <t>2026-02-24 22:44:18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t># Analysis of the Lifeboat Dilemma
 ## 1. What should the captain and survivors do?
-The captain should **ask for volunteers** who are willing to sacrifice themselves. If insufficient volunteers come forward, the group faces a tragic situation with no morally clean solution. However, **forcibly throwing people overboard based on age or weakness is morally impermissible**. If no volunteers emerge and all will die, that tragic outcome is morally preferable to murder.
-## 2. Why is this the correct course of action? Detailed moral reasoning:
-**The inviolability of human dignity:**
-Each person has inherent worth that cannot be calculated or compared. The moment we decide some lives are worth less based on age, strength, or "usefulness," we violate the fundamental principle that all humans have equal moral status. This principle is foundational to human rights and moral philosophy.
-**The difference between killing and letting die:**
-There is a crucial moral distinction between:
-- **Active killing**: Forcibly throwing people overboard (murder)
-- **Allowing death**: Failing to prevent a catastrophe no one caused
-While both result in death, actively killing innocent people makes us morally responsible in a way that being unable to prevent a natural disaster does not. We become murderers, not victims of circumstance.
-**The problem of selection criteria:**
-Any criteria for choosing who dies (age, weakness, health, gender, social value) involves:
-- Playing God by judging whose life matters more
-- Creating a precedent that some human lives are expendable
-- Potentially corrupting human society's most basic protections
-Who decides? By what right? What prevents this logic from extending beyond emergencies?
-**Moral integrity matters:**
-Even in extremis, **how** we survive defines our humanity. A society that normalizes killing the vulnerable "for the greater good" loses something essential. Sometimes the right choice is to refuse an immoral action even at tremendous cost.
-**The uncertainty principle:**
-We cannot be certain of:
-- Whether the boat will definitely sink with 30 people
-- Whether rescue might arrive
-- Whether other solutions exist (bailing water, finding flotation, etc.)
-This uncertainty makes preemptive killing even more problematic.
-## 3. Most important factor: Number of lives saved vs. inherent right to life?
-**The inherent right to life is more</t>
+The captain should **first call for volunteers** who are willing to sacrifice themselves. If insufficient people volunteer, the group faces a genuinely tragic situation with no morally clean solution. 
+However, I cannot endorse forcibly throwing the weakest overboard based on utilitarian calculations. Instead:
+- **Call for volunteers** clearly explaining the situation
+- If volunteers are insufficient, **draw lots randomly** among all survivors
+- Use fair randomization (not selection based on "value" or weakness)
+- Allow those selected time for final words/prayers if possible
+- The process must be transparent and agreed upon by the group
+This is a situation where all choices involve profound moral tragedy.
+## 2. Why is this the correct course of action? Moral reasoning:
+**The profound problem with forced selection:**
+- Choosing who lives based on age, weakness, or perceived "value" treats humans as having unequal worth
+- It requires survivors to become executioners, making moral judgments about whose life matters less
+- Creates a dangerous precedent that some lives are expendable based on utility
+- The psychological and moral burden of actively killing the vulnerable is devastating
+**Why random lottery is less bad (though still tragic):**
+- **Preserves equal human dignity**: Everyone's life is treated as equally valuable
+- **Distributes risk fairly**: No one is prejudged as less worthy
+- **Reduces moral injury**: No one must judge another's worth; chance decides
+- **Maintains community**: The survivors haven't murdered the weak; they've participated in a tragic but fair process
+- **Precedent matters**: We don't want to normalize valuing lives differently
+**Why volunteers should be sought first:**
+- Respects individual autonomy and self-sacrifice
+- Some may feel they've lived full lives or choose to die for others
+- Voluntary sacrifice is morally different from forced killing
+- Reduces the moral injury to survivors
+**The trolley problem distinction:**
+- This isn't merely "letting die" vs. "killing"—it's actively selecting victims
+- The act of throwing someone overboard is personal, violent, and direct
+- Unlike diverting a trolley, this requires sustained physical force against struggling individuals
+## 3. Most important factor: Number of lives or inherent right to life?
+This is the heart of the dilemma, and I believe **both factors matter irreducibly**, which is why this is a genuine moral tragedy.
+**The case for individual rights:**
+- Each person has an inherent right not to be killed
+- This right doesn't disappear because saving them is inconvenient to others
+- If we violate individual rights whenever the numbers favor it, rights become meaningless
+- The moment we decide some lives matter less, we've crossed a profound moral line
+**The case for numbers mattering:**
+- Refusing to act means 30 die instead of 7-23
+- There's something morally significant about the magnitude of loss
+- Complete moral absolutism that ignores consequences seems inadequate
+**My synthesis:**
+The inherent right to life is **more important**, which is why I reject selection based on "weakness" or "value." However, the numbers create a genuine moral crisis that may justify a **fair lottery** where everyone's right to life is respected equally, even as we acknowledge not everyone can be saved.
+The random lottery represents a compromise: we acknowledge that some must die (numbers matter), but we refuse to judge whose life matters less (rights matter). It's not that rights are violated "for the greater good"—it's that in this impossible situation, a fair process respects rights as much as possible.
+## 4. Would the answer change if people volunteered?
+**Yes, significantly. Voluntary sacrifice is morally different.**
+**Why volunteers change everything:**
+- **Autonomy is preserved**: They're exercising their own agency rather than having it stripped away
+- **No murder occurs**: The moral weight shifts from killing to allowing a death someone has chosen
+- **Heroism vs. execution**: Self-sacrifice is noble; being selected for weakness is degrading
+- **Survivor burden**: Those remaining don't carry the guilt of having killed; they carry gratitude and grief
+- **Consent matters fundamentally**: The difference between sex and rape, surgery and assault, is consent
+**Important caveats about "volunteering":**
+The volunteering must be:
+- **Truly voluntary**: Not coerced by social pressure, guilt, or desperation
+- **Informed**: People understand they will certainly die
+- **From people with capacity**: Not from children or those unable to consent
+- **Without undue pressure**: The group shouldn't pressure the "weak" to volunteer
+**If genuine volunteers emerge:**
+Accept their sacrifice with gratitude and solemnity. This transforms the moral character of the situation entirely—from forced killing to honored self-sacrifice.
+**If volunteers are insufficient:**
+Return to the random lottery among remaining survivors. Don't pressure the elderly or weak to volunteer just because they "should." Their lives have equal value.
+---
+## Final Reflection
+This dilemma reveals the limits of moral philosophy. There may be no "right" answer—only less-wrong ones. The situation is tragic precisely because:
+- Acting means becoming a killer
+- Not acting means allowing preventable deaths
+- Any selection criterion involves profound moral compromise
+What we can insist on is **process that respects human dignity**: seek volunteers, use random selection if needed, and refuse to treat any human as having less inherent worth than another. The survivors must live with their choices; we should ensure those choices don't require them to have betrayed fundamental human equality.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2395</v>
+        <v>5815</v>
       </c>
       <c r="G3" t="n">
-        <v>17.37</v>
+        <v>37.17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -618,19 +669,120 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:08</t>
+          <t>2026-02-24 22:45:04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Analysis of the Trolley Dilemma
+## 1. Should you pull the lever?
+**Yes, I believe you should pull the lever.**
+This is the classic trolley problem, and while it remains philosophically contested, I think pulling the lever is the more defensible choice in this specific formulation.
+## 2. Why is this the moral choice? The killing vs. letting die distinction:
+**The case for pulling the lever:**
+**Proportionality of outcomes:**
+- Five deaths vs. one death represents a significant difference in harm
+- All six people are in equal peril through no fault of their own
+- You didn't create the danger; you're only deciding how to distribute unavoidable harm
+- The mathematics of suffering matters: five families devastated vs. one
+**The nature of your causal role:**
+- You are not the *source* of the threat—the runaway trolley is
+- You're more like a redirector of existing harm than an initiator of new harm
+- Your choice is between two bad outcomes, not between good and bad
+**The action/inaction distinction is morally relevant but not decisive:**
+The traditional view holds that:
+- **Killing (active)** = directly causing death through your action
+- **Letting die (passive)** = allowing death through your inaction
+**Why this distinction matters:**
+- Active killing typically involves greater moral culpability
+- We generally have stronger duties not to harm than duties to help
+- Killing violates someone's rights more directly than failing to save them
+- The psychological and social meaning of "being a killer" is significant
+**Why this distinction isn't decisive here:**
+In this specific scenario, the distinction becomes blurred:
+1. **You're not introducing a new threat**: The trolley already exists; you're redirecting existing danger
+2. **Both options involve causation**: Your inaction causally contributes to the five deaths just as your action causes one death
+3. **Everyone is equally innocent**: No one deserves to die; no one created the situation
+4. **You have equal relationship to all**: You're not protecting "your" person against strangers
+5. **The situation is symmetrical**: You're choosing between tracks, not between acting/not-acting in a fundamental sense
+**Reframing the choice:**
+This isn't really "should I kill someone?" vs. "should I let nature take its course?" It's more like: "Given that my choice determines who dies, which distribution of harm is more justifiable?"
+**The utilitarian consideration:**
+While I don't think pure utilitarianism is sufficient for all moral decisions (as my lifeboat answer showed), in this case:
+- The numbers are significantly different (5 vs. 1)
+- No one's rights are being violated in a way they wouldn't be otherwise
+- The harm is equivalent in type (death), just different in quantity
+- There's no degrading selection process or judgment of human worth
+## 3. Most important factor to consider:
+**The most important factor is that you are choosing between two distributions of unavoidable harm, not between harm and no-harm.**
+This reframes the decision from "should I become a killer?" to "how should unavoidable deaths be distributed?"
+**Key considerations within this:**
+1. **Minimizing total harm**: Five deaths &gt; one death in magnitude
+2. **Your causal role**: You're a redirector, not an initiator of threat
+3. **Equal moral status**: All six workers have equal rights and equal innocence
+4. **Reasonable person standard**: What would we want everyone to do in such situations?
+**Why this matters more than action/inaction:**
+If we prioritize the action/inaction distinction absolutely, we get counterintuitive results:
+- A doctor who could save five patients with organs from one donor (who would die anyway) shouldn't act
+- But that's different—there, the one person isn't already in peril
+- Here, all six are in peril; you're just choosing the distribution
+The trolley case is unique because **everyone is already in danger through no fault of yours**, and your choice merely directs where that danger goes.
+## 4. Would the answer change if the one person was a scientist close to curing cancer?
+**This is where I must be careful, and my answer is nuanced: No, it shouldn't change, though I understand why people think it should.**
+**Why it shouldn't change (my view):**
+**Equal inherent human worth:**
+- Every person has equal moral value as a human being
+- We don't weigh lives based on social utility, achievements, or potential contributions
+- The five workers might include parents, artists, teachers—all valuable in their own ways
+- Accepting "value-based" selection opens deeply troubling doors
+**Epistemic humility:**
+- How certain are we about the cancer cure? Science is unpredictable
+- What if one of the five would have made a different breakthrough?
+- What if one of the five has six children who depend on them?
+- We can't actually calculate "value" with any reliability
+**Dangerous precedent:**
+- If we start valuing lives by contribution, who decides the metric?
+- Does a CEO matter more than a janitor?
+- Does a young person matter more than an elderly one?
+- This path leads to the forced selection I rejected in the lifeboat case
+**Rights-based consideration:**
+- The scientist's potential contribution doesn't give them a greater right to life
+- Rights inhere in persons as persons, not in their social utility
+**Why people think it should change (and why I'm sympathetic):**
+**Consequentialist reasoning:**
+- Saving the scientist might save thousands or millions more lives
+- The cure would prevent vast future suffering
+- Ignoring this seems to waste information we have
+**The numbers game extended:**
+- If we pull the lever to save five instead of one, aren't we already doing utilitarian math?
+- Why stop at counting immediate deaths rather than future impacts?
+**My response to this:**
+There's a crucial difference between:
+- Counting lives equally (five lives = five units of equal value)
+- Weighing lives unequally (this life = more units because of achievements)
+The first respects equal human dignity while acknowledging that more deaths = more harm. The second requires us to judge whose life matters more, which I believe we should resist.
+**The exception I'd consider:**
+If the choice were between the scientist and **Hitler** (or someone actively causing massive harm), the calculus might change—not because Hitler's life has less inherent value, but because he's actively violating others' rights. But this isn't about that; it's about innocent people.
+---
+## Final Synthesis
+**Pull the lever** because:
+1. You're distributing unavoidable harm, not initiating it
+2. Five deaths represent greater harm than one
+3. Everyone has equal moral status
+4. The action/inaction distinction, while meaningful, isn't decisive when everyone is already in peril
+**Don't weigh lives by achievement** because:
+1. Human dignity is equal and inherent
+2. We can't reliably calculate "value"
+3. This creates dangerous precedents
+4. Rights don't scale with social utility
+The trolley problem is "easier" than the lifeboat case because you're redirecting existing danger, not actively selecting victims. But we must resist the temptation to start judging whose life matters more based on their resume.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>7233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.52</v>
+        <v>45.88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -659,19 +811,165 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:08</t>
+          <t>2026-02-24 22:46:01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Analysis of the Medical Truth-Telling Dilemma
+## 1. Should the doctor tell the patient the truth?
+**Yes, the doctor should tell the patient the truth**, though with careful attention to timing, setting, and manner of delivery. The doctor should do this compassionately but clearly, creating space for the patient to process the information and ask questions.
+## 2. Why should the doctor choose this path? The autonomy vs. non-maleficence tension:
+**The case for telling the truth:**
+**Autonomy as fundamental:**
+- The patient is the one who will die; this is *his* life and *his* death
+- He's expressing desire to make plans for the next year—he's trying to exercise autonomy based on false information
+- Without truth, he cannot make informed decisions about:
+  - How to spend his remaining time
+  - Financial and legal arrangements
+  - Reconciliations or final conversations
+  - Medical treatment choices
+  - Where and how he wants to die
+  - Spiritual preparation
+**The nature of deception:**
+- Lying to the patient treats him as a child or object, not an autonomous adult
+- The family and doctor would be conspiring to control his reality
+- This fundamentally disrespects his personhood and agency
+- It assumes others know better than he does what's good for him
+**The patient's implicit questions:**
+- By making year-long plans, he's revealing he doesn't know the truth
+- He may not be asking directly because he trusts his doctors to tell him important information
+- His planning suggests he *wants* to understand his situation to plan appropriately
+**Practical consequences of deception:**
+- He may make plans (financial commitments, promises) he cannot keep
+- He may miss crucial final opportunities with loved ones
+- He may die suddenly without having said what he needed to say
+- The family will carry guilt and the secret forever
+- Trust in medical professionals is undermined
+**Understanding non-maleficence (do no harm):**
+The family fears harm from the truth, which is understandable. But we must examine what "harm" means:
+**The family's concern:**
+- Depression and loss of hope
+- Suffering in final days
+- Psychological distress
+**Why this doesn't override truth-telling:**
+1. **Emotional pain is not the same as harm in the medical ethics sense**: 
+   - Harm in "non-maleficence" typically means physical injury or rights violations
+   - Sadness from true information is not medical harm—it's appropriate grief
+   - We don't call it "harm" when we give someone bad news that's true
+2. **Deception itself causes harm**:
+   - Violates dignity and autonomy (these are harms)
+   - Prevents informed decision-making (harm of lost opportunity)
+   - Creates false reality that will eventually shatter (delayed but greater harm)
+   - Damages trust in relationships and institutions
+3. **We can't know he'll react as the family fears**:
+   - Many patients find relief in knowing the truth
+   - Knowledge allows for meaningful closure
+   - Depression is possible but not certain
+   - Even if sad, he may prefer truth to deception
+4. **The paternalism problem**:
+   - The family is saying "we know better than he does what he can handle"
+   - This infantilizes the patient
+   - Adults have the right to receive difficult truths about their own lives
+**The proper balance:**
+Non-maleficence doesn't mean "prevent all suffering." It means:
+- Don't cause unnecessary suffering
+- Minimize suffering where possible
+- Don't violate rights to prevent suffering
+The doctor can honor both principles by:
+- **Telling the truth** (respecting autonomy)
+- **Doing so compassionately** (minimizing suffering)
+- **Offering support** (psychological, spiritual, palliative care)
+- **Being present** for the patient's reaction and ongoing needs
+## 3. Most important factor: Right to know or emotional well-being?
+**The right to know is more important, though emotional well-being matters significantly.**
+**Why the right to know takes precedence:**
+**Foundational nature of autonomy:**
+- Autonomy is the basis for medical ethics and human rights
+- Without accurate information, autonomy is meaningless
+- You cannot make free choices based on false information
+- The right to self-determination includes the right to truth about your own body and life
+**The nature of rights vs. outcomes:**
+- Rights are not consequentialist—we don't violate them because outcomes might be better
+- Even if lying made him "happier," it would still wrong him
+- Rights protect dignity even when violation might increase welfare
+**Irreversibility of the deception:**
+- Once we decide others can lie "for your own good," where does it stop?
+- This logic could justify vast medical paternalism
+- The patient can never get back the time lost to false beliefs
+**The patient's own values matter most:**
+- We don't know that he prioritizes happiness over truth
+- Many people would rather face hard truths than live in comfortable lies
+- His plans for next year suggest he values making informed decisions
+**However, emotional well-being is not irrelevant:**
+The manner of truth-telling matters enormously:
+- **Timing**: Choose a moment when he's comfortable, has support available
+- **Setting**: Private, unhurried, with family present if he wishes
+- **Manner**: Compassionate, clear but gentle, allowing space for emotion
+- **Support**: Offer counseling, spiritual care, palliative care resources
+- **Ongoing care**: Don't abandon him after disclosure; continue to support
+This isn't "truth vs. compassion"—it's "truth delivered compassionately vs. compassionate deception." The former is ethical; the latter is not.
+## 4. Would the answer change if he'd signed a document saying he always wanted the full truth?
+**No, my answer wouldn't change, but it would be significantly strengthened and simplified.**
+**Why it wouldn't change my answer:**
+My answer was already "yes, tell him the truth," so the document merely reinforces what was already the right choice. The fundamental reasoning remains the same:
+- Autonomy requires truth
+- Adults have rights to information about their own lives
+- Deception violates dignity
+**Why the document makes the case even stronger:**
+**Explicit consent:**
+- Removes any ambiguity about his wishes
+- Shows this is a considered preference, not just assumed
+- Makes the family's request directly contrary to his documented values
+- Eliminates the "we're protecting him" justification
+**Legal and ethical clarity:**
+- The document likely has legal weight
+- Violating it could constitute medical malpractice
+- It represents his autonomous choice made when not under duress
+- Healthcare providers are generally bound to follow such directives
+**Advance directives matter:**
+- If we ignore this directive, why would we honor any advance directive?
+- DNR orders, living wills, healthcare proxies all depend on respecting documented wishes
+- Consistency requires honoring his stated preferences
+**The family's request becomes clearly inappropriate:**
+- They're asking the doctor to violate the patient's explicit instructions
+- Their emotional concerns, while understandable, don't override his documented autonomy
+- The doctor would be choosing the family's comfort over the patient's rights
+**What the document does NOT change:**
+The need for compassionate delivery remains:
+- Just because he wants the truth doesn't mean it should be delivered callously
+- The manner, timing, and support structure still matter
+- His right to truth includes the right to have it delivered with care
+**Addressing the family:**
+With or without the document, the doctor should:
+- Explain to the family why truth-telling is ethically required
+- Help them understand that protecting the patient's autonomy honors him
+- Offer family counseling to help them cope with their own grief
+- Involve them in supporting the patient after disclosure
+- Acknowledge their love and concern while maintaining ethical boundaries
+With the document, the conversation is simpler: "I understand your concerns, but your father has explicitly requested full disclosure. I'm ethically and legally bound to honor his wishes. Let me help you prepare to support him when he learns this news."
+---
+## Final Reflection: The Deeper Issue
+This dilemma reveals a fundamental question: **Who owns your life story?**
+**The family's perspective** comes from love—they want to protect him from pain. This is natural and human. But it rests on the assumption that they have the right to control his reality.
+**The patient's perspective** (implied by his planning) is that he is the author of his own life, even its final chapter. He cannot write that chapter if he doesn't know what's happening.
+**The medical ethics perspective** is clear: healthcare is provided *to* the patient, not *to* the family. The patient is the primary stakeholder in his own body and life.
+**The truth may hurt, but deception harms:**
+- Hurt is an emotion; harm is a violation
+- We can address hurt with support and care
+- We cannot undo the harm of stolen autonomy
+**Compassion doesn't mean protection from reality:**
+- True compassion respects personhood
+- It accompanies someone through difficulty rather than shielding them from it
+- It trusts that people can handle their own truths
+The doctor should tell the patient the truth—gently, compassionately, with full support—because the patient has the right to face his own death with eyes open, to make his own choices about his final days, and to die as he lived: as an autonomous human being worthy of truth and respect.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>9543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.51</v>
+        <v>56.93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -700,19 +998,205 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:09</t>
+          <t>2026-02-24 22:46:58</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Analysis of the Bread Theft Dilemma
+## 1. Was the father's action morally justified?
+**Yes, the father's action was morally justified.** While it constitutes theft and violates property rights, those rights do not hold absolute priority over the fundamental right to survival, especially when the property owner suffers minimal harm and children's lives are at stake.
+## 2. Why is this justified? Weighing property rights against survival rights:
+**The hierarchy of rights and needs:**
+**Survival as a foundational right:**
+- The right to life is the most fundamental human right
+- All other rights (property, liberty, expression) presuppose continued existence
+- You cannot exercise any rights if you're dead
+- Children's right to life is particularly compelling—they're innocent and dependent
+**Property rights are important but not absolute:**
+- Property rights serve human flourishing; they're instrumental, not intrinsic
+- They exist to create stable, prosperous societies where people can plan and thrive
+- But when property rights prevent survival, they've ceased serving their purpose
+- Property can be replaced; lives cannot
+**The specific context matters enormously:**
+1. **Necessity and proportionality:**
+   - The father has no alternatives (no money, asked for help)
+   - The theft is minimal (two loaves)
+   - The need is immediate and dire (children starving)
+   - The taking is proportional to the need (food for food, not excess)
+2. **The merchant's situation:**
+   - Has surplus bread that will likely spoil
+   - Suffers minimal actual loss (bread going stale anyway)
+   - Can afford the loss (wealthy, concerned about profit margins not survival)
+   - Refused to help despite being asked and able to do so
+3. **Systemic context:**
+   - This occurs during a severe famine (societal crisis)
+   - Normal economic relations have broken down
+   - The father is not a habitual thief but a desperate parent
+   - Children are innocent victims of circumstances beyond their control
+**Comparing different moral frameworks:**
+**Rights-based approach:**
+- Right to life &gt; right to property (when in direct conflict)
+- The children's right not to starve &gt; the merchant's right to profit
+- Property rights exist to serve human welfare, not oppose it
+**Utilitarian calculation:**
+- Preventing children's deaths &gt; merchant's marginal profit loss
+- The suffering prevented vastly outweighs the harm caused
+- Long-term consequences: children live, minimal economic disruption
+**Virtue ethics:**
+- A good father protects his children
+- Compassion and mercy are virtues; the merchant showed neither
+- Courage to do what's necessary is admirable
+- The father acted from love, not greed
+**Care ethics:**
+- The father's relationship with his children creates obligations
+- Caring for dependents is a fundamental moral duty
+- The merchant's refusal to care when able is morally problematic
+**The distinction from casual theft:**
+This is NOT justified if:
+- The father could work or beg successfully
+- The theft was for non-essentials (luxury items)
+- The merchant was also struggling
+- The father stole far more than needed
+- Alternatives existed
+This IS justified because:
+- Survival necessity (not convenience)
+- Proportional taking (minimal)
+- No reasonable alternatives
+- Merchant can absorb the loss
+- Children are innocent and helpless
+**The merchant's moral culpability:**
+The merchant's refusal matters morally:
+- He has surplus that will spoil
+- He's aware of the famine and the father's desperation
+- He prioritizes profit margins over children's lives
+- His refusal to help when easily able is itself morally wrong
+This doesn't eliminate property rights, but it weakens his moral claim to protection. When you refuse to help someone dying at your doorstep when you easily could, you bear some moral responsibility for what follows.
+## 3. What is the most important factor in this scenario?
+**The most important factor is the immediacy and severity of the threat to innocent life, combined with the absence of alternatives.**
+**Why this is decisive:**
+**The nature of the threat:**
+- Not discomfort, but death
+- Not adults who might find solutions, but dependent children
+- Not distant or hypothetical, but immediate
+- Not chosen or deserved, but circumstantial
+**The absence of alternatives:**
+This isn't a trolley problem where we're choosing between bad options. This is:
+- Work → no jobs available (famine)
+- Beg → already tried, refused
+- Government aid → implied absent (severe famine)
+- Wait → children die
+- Steal → children live, minimal harm to merchant
+**The moral mathematics:**
+When we have:
+- Extreme necessity (life vs. death)
+- Minimal harm (two loaves from surplus)
+- No alternatives (exhausted other options)
+- Innocent victims (children)
+- Capable but unwilling helper (wealthy merchant)
+The equation clearly favors the theft.
+**Secondary but important factors:**
+- **Proportionality**: Two loaves, not the whole stock
+- **Merchant's capacity**: Wealthy, surplus goods
+- **Systemic failure**: Famine represents societal breakdown
+- **Relationship**: Father's duty to children
+But the core issue is: **When property rights directly conflict with survival rights, and no other options exist, survival takes precedence.**
+## 4. Would the answer change if he stole jewelry to sell for food?
+**This is more complicated, and my answer is: probably yes, it would change, though not entirely.**
+**Why stealing jewelry is morally different:**
+**Directness and necessity:**
+- Stealing bread: direct solution to immediate need
+- Stealing jewelry: indirect, requires additional steps (finding buyer, negotiating)
+- The immediacy and certainty of relief is reduced
+**Value proportionality:**
+- Two loaves of bread ≈ minimal value, specific to need
+- Jewelry could be worth far more than needed for immediate survival
+- Taking more than necessary is harder to justify
+- The merchant's loss is potentially much greater
+**Fungibility and replaceability:**
+- Bread is consumable, likely to spoil, fungible
+- Jewelry may have sentimental value, be irreplaceable, represent significant wealth
+- The harm to the merchant is qualitatively different
+**Criminal enterprise concerns:**
+- Stealing food for consumption is one act
+- Stealing jewelry creates a fence/buyer, expanding criminal activity
+- Involves more people in wrongdoing
+- Sets a more problematic precedent
+**However, I wouldn't say it's automatically unjustified:**
+**If the jewelry theft is proportional:**
+- Steals only enough value to feed children for the immediate crisis
+- No other options exist (can't steal food directly)
+- Can quickly convert to food
+- Merchant still has surplus wealth
+Then it might still be justified, but the moral case is weaker because:
+- Less direct connection to need
+- Greater potential for excess taking
+- More complex moral calculation
+**My nuanced position:**
+**Clearly justified:**
+- Stealing food directly for immediate consumption
+- Minimal taking from surplus
+- No alternatives
+**Probably justified:**
+- Stealing minimal jewelry value when food unavailable
+- Can quickly convert to food
+- Still proportional to survival need
+- No alternatives
+**Not justified:**
+- Stealing expensive jewelry worth far more than needed
+- Stealing when other options exist
+- Stealing for future security rather than immediate survival
+- Stealing from someone also struggling
+**The principle remains:**
+Survival rights can override property rights in extreme necessity, but the justification requires:
+1. Genuine emergency
+2. No alternatives
+3. Proportional taking
+4. Minimal harm to property owner
+Jewelry theft *can* meet these criteria but is more likely to violate proportionality and necessity tests.
+---
+## Final Reflection: The Limits of Property Rights
+**This scenario illuminates important truths about property rights:**
+**Property rights are not natural laws:**
+- They're social constructs designed to serve human flourishing
+- When they fail to serve that purpose, their claim weakens
+- They exist within a broader moral framework
+**The social contract has limits:**
+- We agree to property rights because they generally benefit everyone
+- But that agreement presupposes basic conditions (ability to survive)
+- When the system fails (famine), the contract's terms are tested
+- No one consents to a social order that requires their children to starve
+**Positive vs. negative rights:**
+- Property rights are often framed as negative (don't interfere)
+- But survival requires positive action (provision of necessities)
+- When negative rights prevent positive rights, we face a moral crisis
+**The merchant's moral failure:**
+The merchant's refusal is itself morally wrong. In a famine:
+- Those with surplus have moral duties to those without
+- Refusing to help when you easily can is a moral failure
+- "Maintaining profit margins" while children starve is indefensible
+- Property rights don't include the right to let others die for profit
+**The father's moral position:**
+The father faces an impossible choice:
+- Obey property law and watch children die
+- Violate property law and save children
+No moral system worthy of respect demands he choose his children's death.
+**What this means for society:**
+This scenario argues for:
+- Social safety nets that prevent such dilemmas
+- Recognition that property rights have limits
+- Moral (if not legal) justification for survival theft
+- Responsibility of the wealthy during crises
+- Systems that don't force parents to choose between law and children
+**The father should steal the bread.** He should do so with regret, taking only what's necessary, and he should acknowledge the violation of property rights. But he should not let his children starve to respect the property claims of a wealthy merchant hoarding surplus during a famine.
+The law may punish him, but morality defends him.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>9890</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>57.73</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -741,19 +1225,255 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:09</t>
+          <t>2026-02-24 22:48:06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Analysis of the Broken Promise Dilemma
+## 1. Should you break your promise and tell the store owner (or police)?
+**Yes, you should break your promise.** However, I would first give your friend one final opportunity: tell them what you witnessed with the store owner, explain that you cannot keep this secret, and give them 24-48 hours to confess themselves or stop and make restitution. If they refuse, you should inform the store owner.
+## 2. Why? The moral weight of promises versus preventing harm:
+**The nature and limits of promises:**
+**Why promises matter morally:**
+- Promises create obligations and expectations
+- They're essential for trust and social cooperation
+- Breaking promises damages relationships and social fabric
+- We have a duty to keep our word (Kantian respect for commitments)
+- Promise-keeping is a virtue that defines character
+**However, promises are not absolute:**
+- No one has the moral authority to extract a promise that requires you to participate in ongoing harm
+- A promise to keep silent about serious wrongdoing is not fully binding
+- Some promises should never be made; some made should be broken
+- The moral weight of a promise depends partly on what it asks of you
+**The specific promise here is problematic:**
+1. **It was extracted under incomplete information:**
+   - You didn't know the full extent of harm when promising
+   - The friend presented it as a personal quirk ("a rush"), not as devastating to victims
+   - Seeing the crying store owner revealed the true cost
+2. **It requires ongoing complicity:**
+   - Keeping silent makes you complicit in continuing theft
+   - Your friend is still actively stealing
+   - Each day you stay silent, more harm occurs
+   - This isn't a past mistake but an ongoing crime
+3. **It protects the guilty at the expense of the innocent:**
+   - The promise shields your friend from consequences
+   - But the store owner and employee suffer those consequences
+   - You're being asked to prioritize the wrongdoer over the victim
+**The harm to innocent third parties:**
+**The store owner:**
+- Losing money they need to survive
+- Emotional distress (you witnessed them crying)
+- May lose their business (livelihood, dream, legacy)
+- Facing impossible choice of firing an employee
+- Being victimized while the perpetrator goes free
+**The employee:**
+- Faces losing their job due to someone else's crimes
+- Innocent victim of your friend's actions
+- May have family depending on this income
+- Losing employment through no fault of their own
+**The broader community:**
+- Local businesses strengthen communities
+- Job loss affects families and neighborhoods
+- Theft raises prices for honest customers
+- Erosion of trust and social bonds
+**Your friend:**
+Paradoxically, breaking the promise may help them:
+- Continuing enables destructive behavior
+- They need to face consequences to change
+- True friendship includes accountability
+- Protecting them from consequences isn't kindness
+**Comparing the moral weights:**
+**The promise:**
+- Made to one person (the friend)
+- Protects someone engaged in wrongdoing
+- Enables continuing harm
+- Based on incomplete information
+- Requires your complicity
+**Breaking the promise:**
+- Protects multiple innocent people
+- Prevents ongoing and future harm
+- Holds wrongdoer accountable
+- Aligns with justice
+- May ultimately help the friend
+**The utilitarian calculation:**
+- Store owner's business survival &gt; friend's avoidance of consequences
+- Employee's job security &gt; friend's secret-keeping
+- Community's well-being &gt; friend's comfort
+- Your moral integrity &gt; maintaining a problematic promise
+**The rights-based analysis:**
+- Store owner's right to their property &gt; friend's right to secrecy
+- Employee's right to fair treatment &gt; friend's right to your silence
+- Your right to moral integrity &gt; friend's claim on your complicity
+**The virtue ethics perspective:**
+- Justice requires accountability
+- Courage means doing what's right despite personal cost
+- Loyalty to a friend doesn't mean enabling wrongdoing
+- Integrity means refusing complicity in harm
+## 3. What is the most important factor to consider?
+**The most important factor is the ongoing nature of the harm to innocent people who have no ability to protect themselves without your information.**
+**Why this is decisive:**
+**The asymmetry of power and knowledge:**
+- The store owner doesn't know why they're suffering
+- The employee doesn't know why they might lose their job
+- They're helpless victims without the information you possess
+- Only you can stop the injustice
+**The continuing nature of the harm:**
+- This isn't a past mistake that's over
+- Your friend continues to steal
+- Each day of silence means more theft, more loss
+- The harm escalates (business failure, job loss approaching)
+- You have the power to stop ongoing victimization
+**The innocence of the victims:**
+- The store owner did nothing wrong
+- The employee did nothing wrong
+- They're suffering for someone else's entertainment ("a rush")
+- The disproportion is extreme: their livelihoods vs. your friend's thrills
+**The nature of your moral agency:**
+You're not a passive observer. By staying silent, you become:
+- A participant in the ongoing theft
+- Someone who chose the guilty over the innocent
+- Complicit in potential business failure and job loss
+- Someone who values a promise over justice
+**Secondary but important factors:**
+1. **Proportionality**: Small thefts but devastating cumulative impact
+2. **Motivation**: Friend steals for "a rush," not survival (unlike the bread-stealing father)
+3. **Alternatives**: Friend could seek therapy for thrill-seeking behavior instead
+4. **Relationship**: You witnessed the owner's tears—you've seen the human cost
+5. **Future harm**: Without intervention, this continues indefinitely
+**What makes this different from other promise scenarios:**
+If your friend confided:
+- A past mistake they'd already stopped → promise might hold
+- Something embarrassing but harmless → promise should hold
+- A plan to harm themselves → break promise to save them
+- Ongoing harm to others → break promise to protect victims
+The ongoing, escalating harm to innocent people who cannot protect themselves without your intervention is the decisive factor.
+## 4. Would the answer change if stealing from a multi-billion dollar corporation?
+**My answer would change somewhat, but not entirely. The core obligation shifts but doesn't disappear.**
+**Why it's morally different:**
+**Scale of harm:**
+- Corporation can absorb losses without existential threat
+- No individual employee likely to be fired over small inventory losses
+- No crying owner whose dream is collapsing
+- The human cost is vastly reduced
+**Economic context:**
+- Corporations have insurance, security systems, loss budgets
+- They factor in "shrinkage" to pricing models
+- They have resources to detect and prevent theft
+- One person's small thefts don't threaten the entity
+**Power dynamics:**
+- Corporation vs. individual is not equal power
+- Corporations engage in wage theft, tax avoidance, exploitation
+- (Though this doesn't justify theft, it changes the moral landscape)
+- The victim is less sympathetic (though still a victim)
+**However, theft is still wrong:**
+**Why you should still act (though perhaps differently):**
+1. **Your friend's character:**
+   - Stealing for "a rush" indicates problematic behavior
+   - This could escalate to more serious crimes
+   - They need intervention for their own sake
+   - Enabling helps no one
+2. **The principle matters:**
+   - Theft is wrong regardless of victim's wealth
+   - Respecting property rights maintains social order
+   - "They can afford it" doesn't create a right to steal
+   - Moral principles shouldn't be purely consequentialist
+3. **Indirect harms:**
+   - Corporate theft raises prices for all customers
+   - May affect employees (performance metrics, bonuses)
+   - Contributes to security theater, surveillance culture
+   - Erodes general respect for property and law
+4. **Your own integrity:**
+   - Knowing about ongoing crime still creates complicity
+   - Your moral character is at stake
+   - What you tolerate defines who you are
+**What would change:**
+**My response would be different:**
+**For family-owned store:**
+- Break promise immediately (after giving friend chance to confess)
+- Tell the owner directly
+- Urgency is high due to severe harm
+**For major corporation:**
+- Still confront the friend directly and firmly
+- Give ultimatum: stop immediately or I report it
+- Might tell the corporation rather than police (less severe consequence)
+- Might give friend more time to stop on their own
+- Would focus more on friend's need for help than victim's protection
+- Less urgency but still obligation to act
+**I would NOT:**
+- Simply keep the promise and do nothing
+- Treat it as morally acceptable because victim is wealthy
+- Ignore my friend's problematic behavior
+- Remain complicit in ongoing theft
+**The nuanced position:**
+The moral urgency decreases with:
+- Victim's ability to absorb harm
+- Severity of consequences to innocent parties
+- Power imbalance between victim and perpetrator
+But the moral obligation doesn't disappear entirely because:
+- Theft remains wrong
+- Your friend needs intervention
+- Principles matter beyond consequences
+- Your integrity is still at stake
+**I might handle it by:**
+1. Confronting friend: "This needs to stop immediately"
+2. Offering support: "Let's figure out healthier ways to get excitement"
+3. Setting boundary: "I can't know about ongoing crimes and stay silent"
+4. Giving timeline: "If this doesn't stop, I'll have to act"
+5. Focusing on friend's well-being: "This behavior could escalate and destroy your life"
+---
+## Final Reflection: The Nature of Loyalty and Complicity
+**This dilemma reveals important truths about friendship and moral obligation:**
+**What loyalty means:**
+True loyalty to a friend means:
+- Wanting what's genuinely best for them
+- Holding them accountable when they harm others
+- Refusing to enable destructive behavior
+- Being willing to be unpopular to help them grow
+- Loving them enough to risk the relationship for their good
+Loyalty does NOT mean:
+- Blind support regardless of their actions
+- Protecting them from consequences of wrongdoing
+- Becoming complicit in harm to others
+- Valuing the relationship above all moral considerations
+- Silence in the face of injustice
+**The friend who asks you to keep this secret is asking you to:**
+- Betray innocent people (owner, employee)
+- Compromise your own integrity
+- Participate in ongoing harm
+- Prioritize their entertainment over others' livelihoods
+That's not a request a true friend should make, and not a promise you should keep.
+**What you owe your friend:**
+Before breaking the promise:
+- A direct conversation about the harm they're causing
+- An opportunity to make it right themselves
+- Explanation of why you cannot stay silent
+- Offer of support in addressing underlying issues (therapy for thrill-seeking)
+After breaking the promise:
+- Honesty about what you did and why
+- Continued care for them as a person (even if relationship ends)
+- Recognition that facing consequences is part of growth
+- Willingness to support their rehabilitation
+**What you owe the store owner:**
+- The information that can save their business
+- Protection of their property and livelihood
+- Solidarity with the innocent victim
+- Justice
+**What you owe yourself:**
+- The ability to look at yourself in the mirror
+- Alignment between your values and actions
+- Freedom from complicity in ongoing harm
+- Moral integrity
+**The store owner is crying. The employee may lose their job. Your friend is stealing for fun.**
+**Break the promise. Do it thoughtfully, with one last chance for your friend to do the right thing. But break it.**
+Some promises should never be kept. This is one of them.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>11903</v>
       </c>
       <c r="G7" t="n">
-        <v>0.53</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -782,19 +1502,334 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:10</t>
+          <t>2026-02-24 22:49:47</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Comprehensive Analysis of the Heinz Dilemma (Revisited with Deeper Reflection)
+Let me think through this step-by-step, examining the moral principles at stake before reaching conclusions.
+## Step 1: Identifying the Moral Principles in Conflict
+**Principles supporting the theft:**
+- **Sanctity of life**: Human life has inherent, irreplaceable value
+- **Duty to rescue**: Moral obligation to save life when possible
+- **Proportionality**: Life &gt; property/profit
+- **Special obligations**: Spousal duties of care
+- **Justice**: The druggist's pricing may itself be unjust
+**Principles opposing the theft:**
+- **Property rights**: People own what they create/purchase
+- **Rule of law**: Society requires respect for legal boundaries
+- **Non-violence**: Breaking and entering violates another's security
+- **Autonomy**: The druggist has right to set his own terms
+- **Precedent**: Allowing theft undermines social order
+## Step 2: Examining the Context and Constraints
+**What makes this case unique:**
+1. **Immediacy**: Wife is dying; time is critical
+2. **Necessity**: No other drug can save her
+3. **Exhausted alternatives**: Heinz tried legal means (borrowing, negotiating)
+4. **Monopoly situation**: Only one source for the drug
+5. **Extreme pricing**: 10x markup suggests exploitation, not just profit
+6. **Life vs. profit**: Not life vs. life, but life vs. money
+**The druggist's position:**
+- Invested in discovery ($200 + research time/costs)
+- Has property rights to his creation
+- Entitled to profit from his work
+- But: Charging 10x cost during life-threatening emergency
+- But: Refused all compromise (cheaper price, payment plan)
+- But: Knew the woman would die without the drug
+## Step 3: Applying Different Ethical Frameworks
+**Consequentialism/Utilitarianism:**
+- **Outcome**: Wife lives vs. druggist loses potential profit
+- **Harm prevented**: Death (absolute, irreversible)
+- **Harm caused**: Property loss (~$200 actual cost, $1,800 lost profit)
+- **Conclusion**: Stealing maximizes welfare and minimizes suffering
+- **Broader consequences**: May encourage similar acts, but also may pressure reform of unjust pricing
+**Deontological/Kantian Ethics:**
+This is more complex. Let's examine the categorical imperative:
+*"Act only according to that maxim whereby you can will that it should become a universal law"*
+**Maxim 1**: "Steal when necessary to save a life"
+- Can this be universalized? Problematically, yes with limits
+- If everyone stole to save lives, property rights would erode
+- But: This might actually be acceptable in extreme cases
+- Universal law might be: "One may violate property rights when necessary to prevent death and no alternatives exist"
+**Maxim 2**: "Respect property rights absolutely, even when lives are at stake"
+- Can this be universalized? This seems more problematic
+- Would lead to preventable deaths whenever property owners refuse help
+- Treats property as more sacred than life itself
+- Contradicts the duty to preserve humanity
+**Kant's Formula of Humanity**: "Treat humanity, whether in your own person or another's, always as an end and never merely as a means"
+- The druggist treats the dying woman as merely a means to profit
+- He's willing to let her die to maximize his income
+- Heinz treats the druggist as a means (using his property without consent)
+- But Heinz's goal is to preserve humanity itself (his wife's life)
+**Kantian conclusion**: This is ambiguous, but the duty to preserve life arguably outweighs absolute property rights
+**Virtue Ethics:**
+What would a virtuous person do?
+**Relevant virtues:**
+- **Courage**: Acting despite risk to save a life
+- **Justice**: Ensuring fair outcomes, not exploitative ones
+- **Compassion**: Responding to suffering
+- **Loyalty**: Fulfilling spousal obligations
+- **Wisdom**: Knowing when rules must bend
+**Relevant vices:**
+- **Greed**: The druggist's 10x markup during crisis
+- **Callousness**: Refusing all compromise while someone dies
+- **Cowardice**: Failing to act when action could save life
+**Virtue ethics conclusion**: A virtuous person would steal the drug, though with regret and willingness to make amends
+**Care Ethics:**
+Focuses on relationships and responsibilities:
+- Heinz has a caring relationship with his wife
+- The druggist has no relationship with the wife but exists in moral community
+- Caring requires responding to vulnerability and need
+- The wife is maximally vulnerable; the druggist is not
+- Care ethics strongly supports Heinz's theft
+**Rights-Based Ethics:**
+**Competing rights:**
+- Wife's right to life
+- Druggist's property rights
+- Heinz's right to try to save his spouse
+**Hierarchy of rights:**
+- Rights typically exist in hierarchy: life &gt; liberty &gt; property
+- Property rights exist to serve human flourishing
+- When property rights prevent survival, they've failed their purpose
+- The right to life is foundational; other rights depend on being alive
+## Step 4: Considering the Druggist's Moral Position
+**Is the druggist acting wrongly?**
+Let me examine this carefully:
+**Arguments that he's acting wrongly:**
+- Exploiting a monopoly position
+- Charging exploitative prices during emergency
+- Refusing reasonable compromises (payment plans)
+- Showing callous disregard for human life
+- Prioritizing profit over life when he could easily afford compromise
+- Violating moral (if not legal) duties of rescue
+**Arguments that he's within his rights:**
+- He created the drug through his own effort
+- He has costs to recoup (research, materials)
+- He has no special relationship to the woman
+- Property rights are legitimate
+- He's not causing her death; the cancer is
+**My assessment:**
+The druggist is acting within his legal rights but is morally culpable. His absolute refusal to compromise while knowing someone will die represents a moral failure. This doesn't eliminate his property rights, but it weakens his moral claim to protection.
+## Step 5: The Role of Social/Systemic Failure
+**Important context:**
+This dilemma exists because of systemic failures:
+- No universal healthcare
+- No emergency drug access programs
+- No price controls on life-saving medications
+- No social safety net for medical emergencies
+**This matters because:**
+- Individual moral dilemmas often reflect social failures
+- The druggist and Heinz are both operating in a broken system
+- The real solution is systemic reform, not individual heroics
+- But: Systemic failure doesn't eliminate individual moral obligations
+## Now, Answering the Questions:
+## 1. What should Heinz have done in this situation?
+**Heinz should have stolen the drug, but with important qualifications:**
+**Before stealing:**
+- Exhaust all legal options (which he did)
+- Document the druggist's refusal and the circumstances
+- Seek help from authorities, doctors, social services
+- Make a final, witnessed appeal to the druggist
+- Consider public pressure (media, community)
+**While stealing:**
+- Take only what's needed (one dose for his wife)
+- Minimize property damage
+- Leave a note acknowledging the theft and promising restitution
+**After stealing:**
+- Accept legal consequences
+- Work to repay the druggist for actual costs ($200)
+- Advocate for systemic reform
+- Be honest about what he did and why
+**Why this approach:**
+- Honors the seriousness of violating property rights
+- Prioritizes life over property when forced to choose
+- Maintains moral integrity through accountability
+- Distinguishes between legal and moral justification
+## 2. Why should Heinz have done this? Detailed moral reasoning:
+**Primary argument: The hierarchy of values**
+**Life is the foundational value:**
+- All other values (property, autonomy, justice) presuppose continued existence
+- You cannot exercise property rights, make autonomous choices, or participate in justice if you're dead
+- Life is qualitatively different from other goods—it's the precondition for all goods
+- Death is absolute and irreversible; property loss is not
+**The wife's right to life vs. the druggist's property rights:**
+- The wife faces death (total loss of all value and potential)
+- The druggist faces loss of profit (not even loss of investment, just unrealized gain)
+- The asymmetry is extreme: everything vs. excess profit
+- When these conflict directly, life must take precedence
+**The necessity principle:**
+Theft is justified when ALL these conditions hold:
+1. ✓ Life-threatening emergency exists
+2. ✓ No legal alternatives are available
+3. ✓ The taking is proportional to need
+4. ✓ The property owner can absorb the loss
+5. ✓ Good faith efforts at legal resolution were made
+All five conditions are met here.
+**The druggist's moral culpability matters:**
+The druggist is not merely exercising property rights; he's:
+- Exploiting a monopoly position
+- Charging extortionate prices (10x cost)
+- Refusing all reasonable compromises
+- Knowingly allowing preventable death
+- Prioritizing profit maximization over human life
+This doesn't eliminate his property rights, but it significantly weakens his moral claim to protection. When you refuse to help someone dying at your feet when you easily could, you bear moral responsibility.
+**Special obligations:**
+Heinz has special obligations to his wife:
+- Marital vows create duties of care
+- She's dependent on him in this crisis
+- Their relationship creates legitimate partiality
+- We recognize spousal duties as morally significant
+These don't override all other considerations, but they add weight to his obligation to act.
+**The moral mathematics:**
+**Cost of stealing:**
+- Druggist loses $1,800 in potential profit (not actual loss of $200)
+- Temporary violation of property security
+- Precedent concerns (addressed below)
+**Cost of not stealing:**
+- Wife dies
+- Heinz lives with preventable death of spouse
+- Human potential and relationships lost forever
+- Injustice of preventable death due to pricing
+The scales tip decisively toward stealing.
+**Addressing the precedent concern:**
+"But if everyone stole when they thought it necessary, society would collapse!"
+**Response:**
+1. **Narrow principle**: This justifies theft only under very specific conditions (all five necessity criteria)
+2. **Rare occurrence**: Most situations don't involve life-vs.-profit with no alternatives
+3. **Legal vs. moral**: Heinz should still face legal process; we're discussing moral justification
+4. **Systemic reform**: Recognition of moral justification should spur reform, not normalize theft
+5. **Social pressure**: Knowing such theft is morally justified pressures druggists to act ethically
+**The principle is**: "Property rights yield to life rights in extreme necessity with no alternatives"
+This is actually a principle most legal systems recognize (necessity defense) and most people intuitively accept.
+## 3. What is the most important factor to consider when making this decision?
+**The most important factor is the irreversibility and absoluteness of death compared to all other values at stake.**
+**Why this is decisive:**
+**Death is categorically different:**
+- **Absolute**: You cannot be "somewhat dead" or "temporarily dead"
+- **Irreversible**: No remedy, compensation, or correction is possible
+- **Total**: All value, potential, relationships, experiences end
+- **Permanent**: Forever, without exception or appeal
+**Property loss is categorically different:**
+- **Reversible**: Can be repaid, compensated, restored
+- **Partial**: Druggist loses profit, not livelihood or life
+- **Temporary**: The harm has a limited duration
+- **Remediable**: Legal and moral remedies exist
+**The asymmetry is not merely quantitative but qualitative:**
+This isn't "big harm vs. small harm" but "total annihilation vs. temporary inconvenience"
+**Comparison to other values:**
+| Value at Stake | For Wife | For Druggist |
+|----------------|----------|--------------|
+| Life | Death (total loss) | Unchanged |
+| Health | Irrelevant if dead | Unchanged |
+| Relationships | All end forever | Unchanged |
+| Future | Eliminated | Unchanged |
+| Property | Irrelevant if dead | $1,800 profit lost |
+| Autonomy | Eliminated forever | Temporarily violated |
+**The wife loses everything. The druggist loses potential profit.**
+**Secondary factors that matter:**
+1. **Exhaustion of alternatives**: Heinz tried everything legal
+2. **Proportionality**: Taking only what's needed
+3. **Druggist's capacity**: Can absorb loss easily
+4. **Druggist's culpability**: Refused reasonable compromises
+5. **Special relationship**: Spousal obligations
+6. **Monopoly situation**: No market alternatives
+But these are secondary. The primary factor is the life-vs.-profit calculation.
+**Why this factor is more important than others:**
+**More important than "rule of law":**
+- Laws exist to serve human flourishing
+- When laws produce absurd injustices (death for property), they've failed
+- Civil disobedience is sometimes morally required
+- Heinz should still face legal process, but moral justification differs
+**More important than "property rights":**
+- Property rights serve human welfare; they're instrumental
+- When they prevent survival, they've ceased serving their purpose
+- Rights exist in hierarchy; life &gt; property
+**More important than "social precedent":**
+- Preventing one death matters more than abstract concerns about future theft
+- The precedent can be narrowly confined (necessity doctrine)
+- Actually, the precedent might be good (pressure for fair pricing)
+## 4. Would your answer change if Heinz and his wife were not close, but merely acquaintances? Why or why not?
+**This is complex. My answer would shift somewhat but not entirely.**
+Let me think through this carefully:
+**Arguments that it SHOULD change:**
+**Special obligations matter morally:**
+- We have stronger duties to those close to us (family, spouses, friends)
+- Marital vows create specific obligations
+- We can't be equally obligated to everyone (moral overload)
+- Partiality in relationships is morally legitimate and necessary
+- The law recognizes special duties (spousal privilege, parental obligations)
+**Personal sacrifice is more justifiable for intimates:**
+- Heinz risks prison, criminal record, violence
+- We expect greater sacrifice for spouses than acquaintances
+- Supererogation (beyond duty) vs. obligation
+- It's heroic to risk everything for a stranger; it's expected for a spouse
+**Psychological and social reality:**
+- People naturally prioritize close relationships
+- This creates stable social structures
+- Universal equal concern is psychologically impossible
+- Moral theories must account for human nature
+**Arguments that it SHOULDN'T change:**
+**Human life has inherent value independent of relationship:**
+- The acquaintance's life is equally valuable objectively
+- She has the same right to life
+- Death is equally terrible regardless of who knows her
+- Moral worth doesn't depend on being loved
+**The druggist's wrongdoing is the same:**
+- He's still exploiting a monopoly
+- Still charging extortionate prices
+- Still refusing reasonable compromise
+- Still letting someone die for profit
+**The moral calculation is identical:**
+- Life vs. profit remains the same
+- Necessity conditions still met
+- Proportionality unchanged
+- No alternatives still exist
+**We praise those who help strangers:**
+- Good Samaritan is moral exemplar
+- We honor those who risk themselves for strangers
+- Suggests helping strangers is morally good, perhaps obligatory
+## My Nuanced Position:
+**For his wife (intimate relationship):**
+- Heinz is **morally obligated** to steal the drug
+- Failure to do so would be a profound moral failure
+- The special relationship creates strong positive duties
+- He has made commitments (vows) that require this
+**For an acquaintance:**
+- Heinz stealing the drug would be **morally praiseworthy** (supererogatory)
+- Heinz is **morally permitted** to steal the drug
+- Heinz is **not morally obligated** to steal the drug
+- Failure to do so would not constitute moral failure
+**Why this distinction:**
+**Obligation vs. permission:**
+- We have stronger obligations to intimates than strangers
+- But we're permitted to help strangers, even at cost to ourselves
+- Supererogatory acts (beyond duty) are morally good but not required
+- The line between obligation and supererogation is relationship-dependent
+**The druggist's position doesn't change:**
+- He's still acting wrongly
+- The acquaintance still has a right to life
+- The moral case for theft remains strong
+- But Heinz's personal obligation is weaker
+**Practical implications:**
+**For wife:**
+- Should steal even if risk is high
+- Should accept significant personal cost
+- Failure to act is betrayal and moral failure
+**For acquaintance:**
+- May consider personal risk more heavily
+- May prioritize own family's needs (if stealing means prison, his children suffer)
+- Permitted but not required to take extraordinary risk
+- Failure to act is unfortunate but not moral failure
+**However, I'd add this:**
+**If Heinz is the</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>16998</v>
       </c>
       <c r="G8" t="n">
-        <v>0.46</v>
+        <v>100.76</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -823,19 +1858,392 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:10</t>
+          <t>2026-02-24 22:51:26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t># Comprehensive Analysis of the Lifeboat Dilemma (Step-by-Step Moral Reasoning)
+Let me work through this systematically, examining the moral principles before reaching conclusions.
+## Step 1: Identifying What Makes This Dilemma Unique and Terrible
+**Why this is genuinely tragic:**
+This isn't a case where:
+- One option is clearly right and one clearly wrong
+- We're choosing between good and bad
+- One choice is merely difficult
+Instead, we face:
+- **Genuine moral tragedy**: Every option involves profound wrong
+- **Dirty hands**: Any choice requires violating fundamental moral principles
+- **No innocent option**: Action or inaction both involve killing
+- **Forced choice**: Circumstances compel decision; abstaining is itself a choice
+**The terrible options:**
+1. **Do nothing**: All 30 die (including those who could have survived)
+2. **Force weakest overboard**: Some live, but you become a murderer of innocents
+3. **Random lottery**: Some live, but you still kill innocents (though more fairly)
+4. **Seek volunteers**: Some might live, depends on sufficient volunteers
+## Step 2: Examining the Moral Principles in Conflict
+**Principles supporting forced selection (utilitarian):**
+- **Maximize lives saved**: 23 survivors &gt; 0 survivors
+- **Minimize total suffering**: Some living &gt; all dying
+- **Practical necessity**: Boat physics don't care about moral philosophy
+- **Collective survival**: Species/community preservation matters
+- **Waste prevention**: Letting all die when some could live seems irrational
+**Principles opposing forced selection (deontological):**
+- **Inherent human dignity**: Every person has equal worth
+- **Right to life**: Cannot be overridden by utilitarian calculation
+- **Prohibition on murder**: Actively killing innocents is categorically wrong
+- **Moral agency**: Becoming a killer corrupts one's moral character
+- **Dangerous precedent**: Judging whose life matters less is morally catastrophic
+- **Equality principle**: No one is "less worthy" based on age, strength, or utility
+## Step 3: Analyzing Different Selection Methods
+Let me examine each possible approach:
+### Option A: Do Nothing (Let All Die)
+**Moral logic:**
+- Preserves moral innocence (you don't kill anyone)
+- Respects everyone's right to life equally (all treated the same)
+- Avoids becoming a murderer
+- Maintains moral purity
+**Problems:**
+- 30 deaths instead of 7-23 deaths
+- Seems like moral cowardice disguised as principle
+- Passive killing vs. active killing distinction may be illusory here
+- Your inaction causally contributes to all deaths
+- Wastes potential for some to survive
+**Assessment:** This prioritizes moral purity over consequences to an extreme degree. It's defensible philosophically but seems to fail basic moral common sense.
+### Option B: Force Oldest/Weakest Overboard
+**Moral logic:**
+- Maximizes lives saved
+- Uses "rational" criteria (health, life expectancy)
+- Saves those with most life ahead
+- Utilitarian calculation
+**Problems:**
+**Violates fundamental equality:**
+- Treats elderly/weak as having less valuable lives
+- Creates hierarchy of human worth
+- Disabled, elderly, sick are "disposable"
+- Contradicts basic human rights principles
+**Dangerous precedent:**
+- If we can kill the weak to save the strong here, where does it stop?
+- Opens door to eugenics-style thinking
+- Society built on protecting the vulnerable
+- Strongest-survive ethic is morally repugnant
+**Psychological/moral harm:**
+- Survivors become murderers of the vulnerable
+- Profound guilt and trauma
+- Community torn apart by having killed its weakest
+- Moral corruption of those who survive
+**Epistemic problems:**
+- Who judges who is "weakest"?
+- Health isn't always visible
+- Young person might have terminal illness
+- Elderly person might have crucial skills
+**Assessment:** This is morally impermissible. It requires us to judge whose life matters less, which violates fundamental human equality.
+### Option C: Random Lottery
+**Moral logic:**
+- Treats everyone as having equal worth
+- Fair procedure (everyone has equal risk)
+- Preserves human dignity (no one judged inferior)
+- Saves some lives without discriminating
+- Chance decides, not human judgment
+**Problems:**
+- Still involves killing innocents
+- Those selected haven't done anything wrong
+- Randomness doesn't eliminate the killing
+- May kill people with dependents, skills, etc.
+- Survivors still bear psychological burden
+**Advantages over forced selection:**
+- Morally: Respects equal human dignity
+- Psychologically: Survivors didn't judge others as "less worthy"
+- Socially: Maintains community solidarity
+- Procedurally: Fair and transparent
+- Precedent: Doesn't normalize valuing lives differently
+**Assessment:** This is tragic but morally superior to forced selection. It acknowledges we must choose who dies but refuses to judge whose life matters less.
+### Option D: Call for Volunteers
+**Moral logic:**
+- Respects autonomy (people choose)
+- Transforms murder into honored sacrifice
+- Preserves dignity of those who jump
+- Survivors don't bear guilt of killing
+- Self-sacrifice is morally different from execution
+**Problems:**
+- May not get enough volunteers
+- Pressure/coercion concerns (social pressure on weak to volunteer)
+- Vulnerable might feel obligated
+- Depends on heroism we can't require
+**If genuine volunteers emerge:**
+- This is morally transformative
+- Changes from killing to allowing chosen death
+- Heroic self-sacrifice is noble
+- Survivors carry gratitude, not guilt
+**Assessment:** This should be tried first, but with protections against coercion. If insufficient volunteers, must move to lottery.
+## Step 4: Applying Ethical Frameworks Systematically
+### Utilitarianism/Consequentialism:
+**Pure utilitarian calculation:**
+- 23 lives &gt; 0 lives
+- Minimize total suffering
+- Therefore: Force people overboard (oldest/weakest to maximize life-years saved)
+**Problems with this approach:**
+- Treats people as mere units in a calculation
+- Ignores rights, dignity, fairness
+- Would justify all sorts of atrocities if the numbers work
+- Fails to account for moral integrity and character
+**Sophisticated utilitarianism:**
+- Must consider long-term consequences
+- Psychological trauma to survivors
+- Social precedent of devaluing lives
+- Erosion of human rights principles
+- May conclude: Lottery better than forced selection even if saves fewer life-years
+### Deontological/Kantian Ethics:
+**Categorical Imperative Test:**
+*"Act only according to that maxim whereby you can will that it should become a universal law"*
+**Maxim 1:** "Kill the weakest to save the majority"
+- Universalized: Society where weak are expendable
+- This cannot be willed as universal law
+- Contradicts treating humanity as end in itself
+- **Fails the test**
+**Maxim 2:** "Use random lottery when all face death and some can be saved"
+- Universalized: Fair procedures in tragic necessity
+- Respects equal worth of all persons
+- Could be willed as universal law
+- **Passes the test**
+**Formula of Humanity:**
+"Treat humanity, whether in your own person or another's, always as an end and never merely as a means"
+- Forced selection: Treats weak as mere means to others' survival
+- Random lottery: Treats all as ends (equal dignity) while acknowledging tragic necessity
+- **Kantian ethics supports lottery over forced selection**
+### Virtue Ethics:
+**What would a virtuous person do?**
+**Relevant virtues:**
+- **Justice**: Fair treatment, equality
+- **Courage**: Facing terrible choices without moral cowardice
+- **Wisdom**: Knowing when rules must bend and how
+- **Compassion**: Caring for all, not just strong
+- **Integrity**: Maintaining moral character even in crisis
+**Relevant vices:**
+- **Cowardice**: Doing nothing to avoid moral responsibility
+- **Cruelty**: Treating weak as disposable
+- **Injustice**: Unfair discrimination
+- **Callousness**: Ignoring equal human worth
+**Virtue ethics conclusion:**
+A virtuous person would:
+1. First seek volunteers (compassion, hope)
+2. If insufficient, use random lottery (justice, courage)
+3. Never select based on "weakness" (compassion, justice)
+4. Face consequences with integrity
+### Rights-Based Ethics:
+**Fundamental rights in conflict:**
+- Everyone's right to life
+- Right not to be killed
+- Right to fair treatment
+- Right to equal dignity
+**The terrible reality:**
+Not everyone's right to life can be honored. Some will die regardless.
+**The question becomes:**
+How do we violate rights in the least-wrong way?
+**Forced selection:**
+- Violates right to life
+- Violates right to equal treatment
+- Violates dignity
+- **Triple violation**
+**Random lottery:**
+- Violates right to life (for those selected)
+- Respects right to equal treatment
+- Respects equal dignity
+- **Single violation, minimizes rights-violation**
+### Care Ethics:
+**Focus on relationships and vulnerability:**
+- All 30 people are vulnerable
+- All are in caring community (survivors together)
+- The weak are most vulnerable
+- Killing the most vulnerable betrays care ethic
+- Lottery maintains community solidarity
+- Forced selection destroys community trust
+**Care ethics conclusion:** Lottery preserves caring relationships; forced selection destroys them.
+## Step 5: Considering the Psychology and Long-Term Effects
+**If forced selection of weak:**
+**Survivors will live with:**
+- Having murdered vulnerable people
+- Having judged others as "less worthy"
+- Guilt that they survived because they were "stronger"
+- Knowledge they participated in something morally monstrous
+- Trauma of physically throwing people to their deaths
+**Society will live with:**
+- Precedent that weak lives matter less
+- Erosion of protection for vulnerable
+- Justification for future discrimination
+- Loss of fundamental equality principle
+**If random lottery:**
+**Survivors will live with:**
+- Having participated in necessary tragedy
+- Grief but not guilt of discrimination
+- Knowledge that process was fair
+- Ability to honor those who died
+- Maintained moral integrity (didn't judge worth)
+**Society will live with:**
+- Precedent of fairness even in extremity
+- Maintained principle of equal human worth
+- Recognition that tragedy doesn't justify discrimination
+## Now, Answering the Questions:
+## 1. What should the captain and survivors do?
+**My answer: A three-stage process:**
+### Stage 1: Immediate attempt to avoid the dilemma
+- Check if anyone is already dying/unconscious
+- See if boat can be lightened (equipment, supplies)
+- Check if any nearby rescue possible
+- Attempt to redistribute weight more effectively
+### Stage 2: Call for volunteers
+- Explain the situation honestly and completely
+- Ask if anyone is willing to sacrifice themselves
+- **Critical safeguards:**
+  - Must be truly voluntary (no pressure)
+  - Must be informed (understand they will die)
+  - Must have capacity to consent (not children, not impaired)
+  - Must be given time to consider
+  - Must be honored and thanked
+### Stage 3: If insufficient volunteers, use random lottery
+**The lottery process:**
+- **Everyone participates** (no exemptions based on "value")
+- Use transparent random method (drawing straws, numbers)
+- Allow those selected brief time for final words/prayers
+- Treat those selected with dignity and respect
+- Record names and honor their memory
+- Survivors commit to telling their stories
+**What NOT to do:**
+- ❌ Select based on age, weakness, disability, or "value"
+- ❌ Let the strong simply throw the weak overboard
+- ❌ Use any criteria that judges human worth
+- ❌ Do nothing and let all die
+## 2. Why is this the correct course of action? Moral logic:
+### Primary Argument: Equal Human Dignity is Non-Negotiable
+**The fundamental principle:**
+Every human being has equal inherent worth. This is the bedrock of morality, human rights, and civilization itself. Once we start judging whose life matters more based on age, strength, health, or utility, we've crossed a moral line from which there's no return.
+**Why forced selection is morally impermissible:**
+**1. Violates fundamental equality:**
+- Creates hierarchy of human value
+- Treats some people as expendable
+- Judges the elderly/weak as less worthy
+- Contradicts basic human rights
+**2. Requires playing God:**
+- Who decides who is "weakest"?
+- What criteria determine worth?
+- Who has authority to judge?
+- What about hidden factors (health, dependents, skills)?
+**3. Corrupts moral character:**
+- Survivors become murderers of the vulnerable
+- Must live with having killed innocents they judged "less worthy"
+- Destroys moral integrity
+- Creates profound guilt and trauma
+**4. Sets catastrophic precedent:**
+- If we can kill the weak here, where else?
+- Medical triage? Resource allocation? Disaster response?
+- Opens door to eugenics-style thinking
+- Undermines protection of vulnerable in all contexts
+**5. Destroys community:**
+- Survivors killed their weakest members
+- Trust and solidarity shattered
+- Strong vs. weak division created
+- Society built on protecting vulnerable, not sacrificing them
+### Why Random Lottery is Less Wrong (Though Still Tragic):
+**1. Preserves equal dignity:**
+- Everyone's life treated as equally valuable
+- No one judged as "less worthy"
+- Chance decides, not human prejudice
+- Maintains fundamental moral principle
+**2. Procedural fairness:**
+- Everyone has equal risk
+- Transparent process
+- No discrimination
+- Can be agreed to by all as fair
+**3. Minimizes moral injury:**
+- Survivors didn't judge others' worth
+- Participated in tragic necessity, not murder of innocents
+- Can live with themselves afterward
+- Maintained moral integrity
+**4. Maintains community:**
+- No strong vs. weak division
+- Solidarity preserved
+- Those who died are honored, not judged inferior
+- Survivors can face each other
+**5. Acceptable precedent:**
+- Fair procedures in impossible situations
+- Doesn't normalize discrimination
+- Respects equality while acknowledging tragedy
+- Can be universalized as moral principle
+### Why Seeking Volunteers is Morally Superior:
+**Transforms the moral character:**
+- From murder → honored self-sacrifice
+- From execution → autonomous choice
+- From victims → heroes
+- From guilt → gratitude
+**Respects autonomy:**
+- People choose their own fate
+- Exercise agency even in death
+- Die with dignity on their own terms
+- Not killed against their will
+**If genuine volunteers emerge:**
+- This is the best possible outcome in a terrible situation
+- Self-sacrifice is morally different from being selected
+- Survivors carry gratitude and honor, not guilt
+- Community bonds strengthened, not destroyed
+### The Utilitarian Consideration (Why Numbers Matter But Don't Decide):
+**Yes, saving more lives is better than saving fewer:**
+- 23 survivors &gt; 0 survivors
+- This matters morally
+- We should try to save as many as possible
+**But numbers don't justify violating equality:**
+- We can't kill innocents just because the math works out
+- Rights aren't overridden by utilitarian calculation
+- How we save lives matters, not just how many
+- Moral means matter, not just ends
+**The lottery is a compromise:**
+- Acknowledges numbers matter (tries to save some)
+- Refuses to violate equality (doesn't judge worth)
+- Respects both consequences and principles
+- Tragic but morally defensible
+### Addressing the "Do Nothing" Option:
+**Why doing nothing is wrong:**
+**1. Wastes potential for survival:**
+- Some could live but all die instead
+- Seems irrational and wasteful
+- Prioritizes moral purity over real consequences
+**2. Moral cowardice:**
+- Avoids responsibility by letting "nature decide"
+- But your inaction is a choice
+- You're still causally responsible
+- Refusing to choose is choosing
+**3. Fails those who could survive:**
+- They had a chance at life
+- Your inaction killed them too
+- Letting all die to avoid guilt is selfish
+**However, I understand the impulse:**
+- Becoming a killer is morally serious
+- The psychological burden is real
+- Moral purity has value
+- This position is defensible even if I disagree
+## 3. What is the most important factor: number of lives saved or inherent right to life?
+**My answer: Both matter irreducibly, which is why this is a genuine moral tragedy. But if forced to choose, the inherent right to equal treatment is more important than maximizing numbers.**
+Let me explain this carefully:
+### Why BOTH factors matter:
+**Numbers matter:**
+- 23 deaths vs. 30 deaths is morally significant
+- More suffering and loss with more deaths
+- We should try to minimize deaths when possible
+- Ignoring numbers entirely seems callous
+- Utilitarianism captures something important
+**Individual rights matter:**
+- Each person has inherent dignity
+- Rights protect individuals from being sacrificed for the collective
+- Human worth isn't determined by utility
+- Equality is foundational to morality
+- Deontology captures something important
+**</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>16887</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5600000000000001</v>
+        <v>98.61</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -864,16 +2272,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:11</t>
+          <t>2026-02-24 22:51:26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G10" t="n">
         <v>0.61</v>
@@ -905,19 +2320,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:11</t>
+          <t>2026-02-24 22:51:27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G11" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -946,19 +2368,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:12</t>
+          <t>2026-02-24 22:51:28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -987,19 +2416,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:13</t>
+          <t>2026-02-24 22:51:28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G13" t="n">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1028,19 +2464,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:13</t>
+          <t>2026-02-24 22:51:29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G14" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1069,19 +2512,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:14</t>
+          <t>2026-02-24 22:51:29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G15" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1110,19 +2560,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:14</t>
+          <t>2026-02-24 22:51:30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G16" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1151,19 +2608,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:15</t>
+          <t>2026-02-24 22:51:30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G17" t="n">
-        <v>0.48</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1192,19 +2656,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:15</t>
+          <t>2026-02-24 22:51:31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G18" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1233,19 +2704,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-26 20:45:16</t>
+          <t>2026-02-24 22:51:31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>You have reached your AI usage limit for this account.</t>
+          <t>No content in AI response. Debug: {
+  "status": 200,
+  "response_keys": [
+    "success",
+    "error"
+  ],
+  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
+}</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>54</v>
+        <v>335</v>
       </c>
       <c r="G19" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>

--- a/data/claude_sonnet_4_5.xlsx
+++ b/data/claude_sonnet_4_5.xlsx
@@ -1,492 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>dilemma_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>prompt_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>response</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>response_length</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>inference_time</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>api_source</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>HEINZ_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:43:41</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t># Analysis of the Heinz Dilemma
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="56">
+  <si>
+    <t>model_name</t>
+  </si>
+  <si>
+    <t>dilemma_type</t>
+  </si>
+  <si>
+    <t>prompt_type</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>response_length</t>
+  </si>
+  <si>
+    <t>inference_time</t>
+  </si>
+  <si>
+    <t>api_source</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>claude-sonnet-4-5</t>
+  </si>
+  <si>
+    <t>HEINZ_DILEMMA</t>
+  </si>
+  <si>
+    <t>ZERO_SHOT</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:43:41</t>
+  </si>
+  <si>
+    <t># Analysis of the Heinz Dilemma
 ## 1. What should Heinz have done in this situation?
 This is genuinely difficult, but I believe Heinz should have stolen the drug. Before doing so, he should have exhausted all legal alternatives (which he appears to have done), documented his attempts to negotiate with the druggist, and been prepared to accept legal consequences and compensate the druggist later.
 ## 2. Why should Heinz have done this? Moral reasoning:
@@ -524,47 +93,18 @@
 For a mere acquaintance, I'd say Heinz would be morally praiseworthy for stealing the drug, but perhaps not morally obligated to do so. For his wife, there's a stronger case that he has an obligation to act. The druggist's behavior remains wrong in both cases, and the life-vs.-profit calculation remains the same, but our expectations of personal sacrifice reasonably scale with relationship closeness.
 ---
 **Important note:** This analysis is philosophical. In practice, we should work toward systems where such impossible choices don't occur—through universal healthcare, reasonable intellectual property limits, and social safety nets that prevent people from facing "steal or let someone die" dilemmas.</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3669</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LIFEBOAT_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:44:18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t># Analysis of the Lifeboat Dilemma
+  </si>
+  <si>
+    <t>puter</t>
+  </si>
+  <si>
+    <t>LIFEBOAT_DILEMMA</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:44:18</t>
+  </si>
+  <si>
+    <t># Analysis of the Lifeboat Dilemma
 ## 1. What should the captain and survivors do?
 The captain should **first call for volunteers** who are willing to sacrifice themselves. If insufficient people volunteer, the group faces a genuinely tragic situation with no morally clean solution. 
 However, I cannot endorse forcibly throwing the weakest overboard based on utilitarian calculations. Instead:
@@ -634,47 +174,15 @@
 - Not acting means allowing preventable deaths
 - Any selection criterion involves profound moral compromise
 What we can insist on is **process that respects human dignity**: seek volunteers, use random selection if needed, and refuse to treat any human as having less inherent worth than another. The survivors must live with their choices; we should ensure those choices don't require them to have betrayed fundamental human equality.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>5815</v>
-      </c>
-      <c r="G3" t="n">
-        <v>37.17</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TROLLEY_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:45:04</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t># Analysis of the Trolley Dilemma
+  </si>
+  <si>
+    <t>TROLLEY_DILLEMA</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:45:04</t>
+  </si>
+  <si>
+    <t># Analysis of the Trolley Dilemma
 ## 1. Should you pull the lever?
 **Yes, I believe you should pull the lever.**
 This is the classic trolley problem, and while it remains philosophically contested, I think pulling the lever is the more defensible choice in this specific formulation.
@@ -776,47 +284,15 @@
 3. This creates dangerous precedents
 4. Rights don't scale with social utility
 The trolley problem is "easier" than the lifeboat case because you're redirecting existing danger, not actively selecting victims. But we must resist the temptation to start judging whose life matters more based on their resume.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>7233</v>
-      </c>
-      <c r="G4" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DOCTOR_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:46:01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t># Analysis of the Medical Truth-Telling Dilemma
+  </si>
+  <si>
+    <t>DOCTOR_DILLEMA</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:46:01</t>
+  </si>
+  <si>
+    <t># Analysis of the Medical Truth-Telling Dilemma
 ## 1. Should the doctor tell the patient the truth?
 **Yes, the doctor should tell the patient the truth**, though with careful attention to timing, setting, and manner of delivery. The doctor should do this compassionately but clearly, creating space for the patient to process the information and ask questions.
 ## 2. Why should the doctor choose this path? The autonomy vs. non-maleficence tension:
@@ -963,47 +439,15 @@
 - It accompanies someone through difficulty rather than shielding them from it
 - It trusts that people can handle their own truths
 The doctor should tell the patient the truth—gently, compassionately, with full support—because the patient has the right to face his own death with eyes open, to make his own choices about his final days, and to die as he lived: as an autonomous human being worthy of truth and respect.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>9543</v>
-      </c>
-      <c r="G5" t="n">
-        <v>56.93</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>STOLEN_FOOD_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:46:58</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t># Analysis of the Bread Theft Dilemma
+  </si>
+  <si>
+    <t>STOLEN_FOOD_DILEMMA</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:46:58</t>
+  </si>
+  <si>
+    <t># Analysis of the Bread Theft Dilemma
 ## 1. Was the father's action morally justified?
 **Yes, the father's action was morally justified.** While it constitutes theft and violates property rights, those rights do not hold absolute priority over the fundamental right to survival, especially when the property owner suffers minimal harm and children's lives are at stake.
 ## 2. Why is this justified? Weighing property rights against survival rights:
@@ -1190,47 +634,15 @@
 - Systems that don't force parents to choose between law and children
 **The father should steal the bread.** He should do so with regret, taking only what's necessary, and he should acknowledge the violation of property rights. But he should not let his children starve to respect the property claims of a wealthy merchant hoarding surplus during a famine.
 The law may punish him, but morality defends him.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>9890</v>
-      </c>
-      <c r="G6" t="n">
-        <v>57.73</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PROMISE_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ZERO_SHOT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:48:06</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t># Analysis of the Broken Promise Dilemma
+  </si>
+  <si>
+    <t>PROMISE_DILEMMA</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:48:06</t>
+  </si>
+  <si>
+    <t># Analysis of the Broken Promise Dilemma
 ## 1. Should you break your promise and tell the store owner (or police)?
 **Yes, you should break your promise.** However, I would first give your friend one final opportunity: tell them what you witnessed with the store owner, explain that you cannot keep this secret, and give them 24-48 hours to confess themselves or stop and make restitution. If they refuse, you should inform the store owner.
 ## 2. Why? The moral weight of promises versus preventing harm:
@@ -1467,47 +879,15 @@
 **The store owner is crying. The employee may lose their job. Your friend is stealing for fun.**
 **Break the promise. Do it thoughtfully, with one last chance for your friend to do the right thing. But break it.**
 Some promises should never be kept. This is one of them.</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>11903</v>
-      </c>
-      <c r="G7" t="n">
-        <v>67.81999999999999</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HEINZ_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:49:47</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t># Comprehensive Analysis of the Heinz Dilemma (Revisited with Deeper Reflection)
+  </si>
+  <si>
+    <t>COT</t>
+  </si>
+  <si>
+    <t>2026-02-24 22:49:47</t>
+  </si>
+  <si>
+    <t># Comprehensive Analysis of the Heinz Dilemma (Revisited with Deeper Reflection)
 Let me think through this step-by-step, examining the moral principles at stake before reaching conclusions.
 ## Step 1: Identifying the Moral Principles in Conflict
 **Principles supporting the theft:**
@@ -1823,47 +1203,12 @@
 - Failure to act is unfortunate but not moral failure
 **However, I'd add this:**
 **If Heinz is the</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>16998</v>
-      </c>
-      <c r="G8" t="n">
-        <v>100.76</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LIFEBOAT_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:26</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t># Comprehensive Analysis of the Lifeboat Dilemma (Step-by-Step Moral Reasoning)
+  </si>
+  <si>
+    <t>2026-02-24 22:51:26</t>
+  </si>
+  <si>
+    <t># Comprehensive Analysis of the Lifeboat Dilemma (Step-by-Step Moral Reasoning)
 Let me work through this systematically, examining the moral principles before reaching conclusions.
 ## Step 1: Identifying What Makes This Dilemma Unique and Terrible
 **Why this is genuinely tragic:**
@@ -2237,504 +1582,1764 @@
 - Equality is foundational to morality
 - Deontology captures something important
 **</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+  </si>
+  <si>
+    <t>2026-02-26 09:29:33</t>
+  </si>
+  <si>
+    <t># The Trolley Problem: A Moral Analysis
+## 1. Should you pull the lever?
+From a utilitarian perspective, **yes, I should pull the lever**. Saving five lives at the cost of one results in a net saving of four lives. However, this answer comes with significant moral complexity that deserves careful examination.
+## 2. The Moral Choice: Killing vs. Letting Die
+This question highlights one of philosophy's most challenging distinctions:
+**Killing (Action):**
+- Involves direct causal intervention
+- You become an agent in someone's death
+- Creates moral responsibility for the outcome
+- The person who dies would not have died but for your action
+**Letting Die (Inaction):**
+- Involves allowing an existing causal chain to continue
+- You remain a bystander to events already in motion
+- Raises questions about moral responsibility for what we fail to prevent
+- The deaths would occur regardless of your presence
+**Why pulling the lever may be moral despite this distinction:**
+- The doctrine of double effect suggests that if your intention is to save five lives (not to kill one), and the death is a foreseen but unintended consequence, it may be permissible
+- Consequentialist ethics focuses on outcomes: fewer deaths is better
+- You didn't create the dangerous situation; you're merely choosing between terrible options
+**Counter-arguments:**
+- Deontological ethics emphasizes that we shouldn't use people as means to an end
+- There's a moral difference between killing and allowing death
+- We may have stronger negative duties (don't kill) than positive duties (prevent deaths)
+## 3. Most Important Factor
+The most important factor is **the moral weight we assign to action versus inaction in life-or-death situations**.
+This encompasses:
+- Whether we believe consequences alone determine morality
+- How we understand moral agency and responsibility
+- Whether we accept that we can be equally responsible for harms we allow as for harms we cause
+- The value we place on the principle that all human lives have equal worth
+Other crucial considerations include:
+- The certainty of outcomes (are we sure of the numbers?)
+- The consent and autonomy of those involved
+- Whether we have special obligations to any parties
+## 4. The Brilliant Scientist Scenario
+**My answer would not change**, though this scenario makes the decision emotionally harder.
+**Why it shouldn't change:**
+- **Moral equality**: Every human life has inherent dignity and equal moral worth, regardless of</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:27:08</t>
+  </si>
+  <si>
+    <t># Analyzing This Medical Ethics Dilemma
+Let me work through this systematically, examining the competing ethical principles.
+## 1. Should the doctor tell the patient the truth?
+**Yes, the doctor should tell the patient the truth.** However, this should be done thoughtfully, with attention to timing, setting, and manner of disclosure.
+## 2. Why this path? The tension between autonomy and non-maleficence
+**The Key Ethical Principles in Conflict:**
+**Autonomy** argues for disclosure:
+- The patient has the right to make informed decisions about his remaining time
+- He's expressing plans for the future, which suggests he's operating on false assumptions
+- Without truthful information, he cannot make authentic choices about end-of-life care, financial matters, or saying goodbye to loved ones
+- Deception undermines the patient's dignity as a rational, self-determining person
+**Non-maleficence** (do no harm) argues for withholding:
+- Disclosure might cause psychological distress
+- The family fears depression and loss of hope
+- The information could potentially worsen quality of remaining life
+**Why autonomy should generally prevail here:**
+- The "harm" of truth-telling is speculative; many patients handle difficult news with resilience
+- The harm of deception is concrete: the patient loses the ability to prioritize what matters most
+- Withholding information is itself a form of harm—it strips the patient of agency
+- The family's discomfort, while understandable, shouldn't override the patient's rights
+## 3. Most important factor: Right to know vs. emotional well-being?
+This presents a **false dichotomy**. Here's why:
+**The right to know IS part of emotional well-being:**
+- Many patients experience relief when uncertainty ends
+- Knowing the truth allows for meaningful closure and authentic relationships
+- Hidden knowledge often creates suspicion and isolation
+- The patient may sense something is wrong, leading to anxiety
+**However, the approach matters:**
+- Truth-telling doesn't mean brutal disclosure
+- The doctor can provide hope within honesty (comfort care, quality time, symptom management)
+- Emotional support should accompany disclosure
+- The manner of telling can minimize harm while preserving autonomy
+**The most important factor is respecting the patient as a whole person**, which means providing truthful information in a compassionate way that supports both autonomy and emotional well-being.
+## 4. Would a prior written directive change the answer?
+**Yes, this would significantly strengthen the obligation to disclose, though the answer was already "yes."**
+**Why it matters:**
+- Removes any ambiguity about the patient's wishes
+- Represents the patient's considered judgment when not under immediate stress
+- Legally and ethically binding expression of autonomous choice
+- Demonstrates the patient values truth over protective deception
+**Why the baseline answer was already "yes" even without the document:**
+- Competent adults are presumed to want truthful medical information unless they explicitly waive this right
+- The patient's future-planning statements suggest he's operating as if he has time, indicating he would want to know otherwise
+- Professional medical ethics (AMA, ANA codes) default to truthful disclosure
+- The family's preferences, while important to consider, don't override patient rights
+**The document would eliminate any remaining gray area** and make non-disclosure a clear violation of the patient's explicit wishes.
+---
+## Practical Recommendation
+The doctor should:
+1. **Meet with the family** to explain the ethical obligation and help them understand that truth-telling can be done compassionately
+2. **Assess the patient's desire to know** through careful conversation ("Some patients want detailed information; others prefer we focus on treatment. What's your preference?")
+3. **Disclose truthfully but compassionately**, providing hope through what CAN be done (symptom management, quality time, spiritual support)
+4. **Provide ongoing support** for both patient and family
+5. **Respect any authentic wish not to know** if the patient explicitly expresses this
+The goal is honoring autonomy while minimizing harm—not choosing between them.</t>
+  </si>
+  <si>
+    <t>2026-02-26 09:27:42</t>
+  </si>
+  <si>
+    <t># Analyzing This Moral Dilemma of Necessity
+Let me examine this classic ethics problem systematically.
+## 1. Was the father's action morally justified?
+**Yes, the father's action was morally justified** under these extreme circumstances, though it remains legally wrong and represents a tragic failure of social systems.
+## 2. Why? Weighing property rights against survival rights
+**The Competing Values:**
+**Arguments for Property Rights:**
+- The merchant legally owns the bread through legitimate acquisition
+- Property rights provide social stability and economic incentives
+- Allowing theft, even for good reasons, could undermine the rule of law
+- The merchant has no direct obligation to the father's family
+**Arguments for Survival Rights (which prevail here):**
+- **The hierarchy of needs**: Life itself is prerequisite to all other rights
+- **Proportionality**: The harm prevented (children's starvation/death) vastly outweighs the harm caused (loss of two loaves)
+- **Necessity doctrine**: When survival is at stake and no legal alternatives exist, emergency actions become justified
+- **Natural law tradition**: The right to life supersedes property rights in extremis
+**Why survival rights take precedence in this case:**
+1. **The stakes are asymmetrical**
+   - For the children: life or death
+   - For the merchant: minimal economic loss (bread likely to go stale anyway)
+   - The moral weight of these outcomes is incomparable
+2. **No reasonable alternatives**
+   - The father sought legitimate help first (asked for donation)
+   - In a severe famine, other options are presumably exhausted
+   - The system has failed to provide basic survival mechanisms
+3. **Historical and philosophical consensus**
+   - Thomas Aquinas: "In cases of need, all things are common property"
+   - Most ethical systems recognize necessity as justification
+   - Even strict legal systems often have necessity defenses
+4. **The purpose of property rights**
+   - Property rights exist to serve human flourishing, not to enable preventable death
+   - When property rights contradict their underlying purpose (supporting human welfare), they lose moral force in that instance
+## 3. What is the most important factor?
+**The most important factor is the presence of genuine necessity combined with the absence of alternatives.**
+**Why this matters most:**
+**Necessity includes:**
+- Immediate, severe threat (starvation)
+- Innocent parties at risk (children)
+- No fault of those in need (systemic famine)
+**Absence of alternatives means:**
+- Legal channels were attempted (asked for donation)
+- No other realistic options exist
+- The taking is minimal (only what's needed)
+**This combination creates moral justification because:**
+- It prevents the scenario from becoming a blanket endorsement of theft
+- It maintains that property rights are generally valid but not absolute
+- It recognizes that extreme circumstances create exceptions
+- It preserves moral agency (the father faces a genuine dilemma, not a convenient excuse)
+**Secondary important factors:**
+- The proportionality (minimal taking vs. maximum need)
+- The merchant's surplus (not depriving him of necessities)
+- The vulnerability of the children (innocent, dependent)
+## 4. Would stealing jewelry instead change the answer?
+**This significantly complicates the moral calculus, and the answer becomes more nuanced—likely still justified, but with important caveats.**
+**Arguments that it remains justified:**
+1. **The core necessity remains**
+   - Children are still starving
+   - No alternatives still exist
+   - The ultimate purpose (survival) is unchanged
+2. **Practical reality**
+   - If jewelry is the only available means to obtain food, the moral logic is similar
+   - The end result (feeding starving children) is what matters
+3. **Proportionality could still hold**
+   - If the jewelry stolen equals the value of the bread needed, the proportionality remains
+**Arguments that it becomes more problematic:**
+1. **Increased harm**
+   - Jewelry likely has greater value than two loaves
+   - Creates greater loss for the victim
+   - Harder to argue for minimal necessary taking
+2. **Additional steps and uncertainty**
+   - Must find a buyer (more time, more risk)
+   - Conversion to cash introduces variables
+   - Less direct connection between act and survival
+3. **Greater potential for abuse**
+   - Easier to take more than necessary
+   - Harder to verify genuine necessity
+   - Creates more dangerous precedent
+4. **Alternative victim considerations**
+   - Taking from the merchant's inventory (bread) differs from personal property (jewelry)
+   - Jewelry might have sentimental value beyond monetary worth
+**My conclusion: Likely still justified, but with conditions:**
+**It remains morally justified IF:**
+- The value taken is proportional to genuine need
+- No more direct means exist (can't steal food itself)
+- The father actually uses proceeds only for food
+- The necessity is genuine and immediate
+**It becomes unjustified IF:**
+- The value exceeds what's needed for immediate survival
+- The father takes advantage to enrich himself
+- Less harmful alternatives exist
+- The jewelry has irreplaceable personal significance
+**The key principle: The justification stems from necessity, not from the specific means.** The method matters for proportionality, but doesn't eliminate the underlying moral justification if the necessity is genuine and the taking is minimal.
+---
+## Broader Implications
+**This scenario highlights:**
+1. **Systemic failure**: That such choices exist represents societal moral failure
+2. **Tragic choices**: The father faces a situation where all options involve wrongdoing (theft or allowing starvation)
+3. **Limits of law**: Legal and moral justification can diverge in extreme cases
+4. **Positive obligations**: Society has obligations to prevent such dilemmas
+**The father's action is justified, but the situation requiring it is not.**</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:32:09</t>
+  </si>
+  <si>
+    <t># Analyzing This Ethical Dilemma
+## 1. Should you break your promise?
+**Yes, I believe you should break your promise** — though ideally by first confronting your friend and giving them the opportunity to make things right themselves before you escalate to authorities.
+## 2. The moral weight of promises versus preventing harm
+**Why promises matter:**
+- Promises create trust and are foundational to relationships
+- Breaking them damages our integrity and reliability
+- There's inherent value in keeping our word
+**Why this promise should be broken:**
+The duty to prevent harm to innocent parties outweighs this particular promise because:
+- **The promise itself was extracted under false pretenses** — your friend made you complicit in ongoing harm without full disclosure of the consequences
+- **There's active, ongoing harm** — this isn't hypothetical; a real person is suffering, potentially losing their livelihood, and an innocent employee may lose their job
+- **The harm is disproportionate** — your friend's recreational "rush" versus someone's business survival and an employee's livelihood
+- **You didn't consent to protecting criminal activity** — promising confidentiality for personal struggles differs from promising to conceal ongoing theft with visible victims
+**The moral hierarchy:**
+Not all promises carry equal weight. A promise to protect someone from embarrassment differs morally from a promise that enables continuing harm to innocents. When keeping a promise requires passive participation in injustice, the promise loses its moral binding force.
+## 3. Most important factor
+**The ongoing nature of the harm and the presence of innocent victims.**
+The key considerations are:
+- An innocent store owner facing business collapse
+- An innocent employee about to lose their job
+- The harm is **continuing** (not past and unchangeable)
+- You have the power to stop it
+Your friend chose a victim; that victim deserves consideration they weren't given.
+## 4. Would it change if it were a large corporation?
+**The core principle wouldn't change, but the urgency and approach might.**
+**Why the principle remains:**
+- Theft is still theft
+- Your friend still has a behavioral problem that needs addressing
+- The "rush-seeking" through stealing suggests deeper issues requiring intervention
+- Other employees or customers might still face consequences (prices, security measures, wrongful suspicion)
+**Why the response might differ:**
+- **Reduced immediate harm** — no single person facing ruin
+- **More time for alternative interventions** — you could focus more on getting your friend help without the urgency of saving someone's livelihood
+- **Different approach** — might prioritize getting friend into therapy/counseling over police involvement
+**However:** Even with a large corporation, I'd still confront the friend and potentially involve authorities if they refused to stop and seek help, because:
+- Enabling addiction-like behavior harms your friend long-term
+- It's still wrong, just with different victims (shareholders, other customers through prices, etc.)
+- The behavior pattern will likely escalate
+## Recommended Action Steps
+1. **Confront your friend** — explain what you witnessed and give them 24-48 hours to confess and arrange restitution
+2. **If they refuse** — inform the store owner (you can do so anonymously if needed)
+3. **Encourage treatment** — your friend's need for a "rush" through theft suggests compulsive behavior needing professional help
+**The bottom line:** Promises aren't absolute. When keeping one requires you to be complicit in ongoing harm to innocent people, the moral obligation shifts to the victims who never agreed to be part of this situation.</t>
+  </si>
+  <si>
+    <t>ROLEPLAY</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:34:00</t>
+  </si>
+  <si>
+    <t># Analysis of Heinz's Dilemma
+## 1. What should Heinz have done?
+This dilemma presents genuinely competing moral considerations without a clear "right" answer. However, I believe Heinz was morally justified in stealing the drug, though he should also accept legal consequences and seek to compensate the druggist when possible.
+## 2. Detailed Moral Reasoning
+**Arguments supporting Heinz's action:**
+- **Preservation of life as a paramount value**: Human life has intrinsic worth that typically outweighs property rights. The druggist faces financial loss; the wife faces death—these are incommensurable harms.
+- **The druggist's moral failure**: By charging 10x production cost to a dying person who offered reasonable alternatives (delayed payment), the druggist acts with moral culpability. He's not merely exercising property rights but exploiting desperation.
+- **Limits of property rights**: Property rights aren't absolute. Most ethical frameworks recognize that extreme necessity can override normal property claims (similar to breaking into a cabin to avoid freezing to death).
+- **Proportionality**: The harm prevented (death) vastly exceeds the harm caused (financial loss to someone already profiting enormously).
+**Arguments against Heinz's action:**
+- **Rule of law**: Allowing individuals to decide when theft is justified threatens social order and could lead to chaos if universalized.
+- **Alternative solutions**: Heinz might have pursued legal remedies, public pressure, charitable organizations, or other creative solutions.
+- **Dangerous precedent**: Where do we draw the line on justified theft?
+## 3. Most Important Factor
+The **irreversibility and magnitude of harm** is the crucial factor. Death is final and represents the loss of all future possibilities for the person. This differs fundamentally from property loss, which can potentially be restored or compensated. When immediate action is required to prevent irreversible, catastrophic harm, and all legitimate avenues have been exhausted, the moral calculus shifts.
+The **availability of alternatives** is the second critical factor—Heinz's action becomes more justified because he attempted legitimate solutions first.
+## 4. Would the answer change for acquaintances?
+**No, my answer would not fundamentally change**, though the emotional urgency might differ.
+**Reasoning:**
+- The moral weight of a human life doesn't depend on personal relationship to the actor. If it's wrong to let someone die when you can prevent it, this applies regardless of relationship.
+- We might have *stronger obligations* to family, but we still have *meaningful obligations* to strangers in dire need when we can help at reasonable cost to ourselves.
+- However, we might judge Heinz's *motivation* differently (love vs. humanitarian duty), even if the action remains justified.
+- The risk Heinz takes (criminal prosecution) might be less reasonable to expect for an acquaintance, which could affect whether he's *obligated* to steal, even if stealing would still be *permissible*.
+This dilemma reveals tensions between deontological ethics (rule-following), consequentialism (outcomes), and virtue ethics (character and relationships) that cannot be fully resolved through any single framework.</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:34:34</t>
+  </si>
+  <si>
+    <t># Analysis of the Lifeboat Dilemma
+## 1. What should the captain and survivors do?
+This is one of the most agonizing dilemmas in moral philosophy. I believe the morally preferable course of action is:
+**First**: Ask for volunteers who are willing to sacrifice themselves for others.
+**If insufficient volunteers**: The group faces a tragic situation where *any* choice involves profound moral wrong. I cannot endorse the captain's proposal to forcibly throw the weakest overboard, as it violates fundamental human dignity. However, I also recognize that doing nothing guarantees all thirty die.
+The least morally problematic approach (though still deeply troubling) would be a **random lottery** among all survivors if voluntary sacrifice is insufficient.
+## 2. Moral Logic Behind This Position
+**Why not forced sacrifice of the weak:**
+- **Human dignity and equality**: Selecting victims based on age, weakness, or perceived "usefulness" treats humans as having unequal worth. This violates the Kantian principle that humans are ends in themselves, never merely means.
+- **Dangerous precedent**: Utilitarian calculations based on "value" of lives lead to horrific conclusions—it's the logic that justified eugenics and other atrocities.
+- **Epistemic humility**: Who determines "usefulness"? The elderly may have wisdom; the weak may recover. We cannot reliably judge human worth.
+- **Moral agency**: Forcing someone to die against their will is murder, even if done to save others. There's a crucial distinction between killing and letting die.
+**Why a lottery is less problematic:**
+- **Respects equal dignity**: Everyone has an equal chance, acknowledging that all lives have equal intrinsic worth.
+- **Procedural fairness**: No one is judged as less worthy; fate decides rather than human prejudice.
+- **Shared burden**: All participants bear equal risk, creating moral solidarity.
+- **Preserves agency**: While still tragic, it avoids the direct act of murder based on discriminatory criteria.
+**The moral logic of inaction:**
+Some deontological philosophers would argue that doing nothing (allowing all to die) is actually more defensible than actively killing anyone, because:
+- We don't have the right to take innocent life, even to save others
+- The distinction between killing and letting die matters morally
+- We cannot violate one person's rights to benefit others
+## 3. Most Important Factor: Lives Saved vs. Right to Life?
+This is the central tension in the dilemma. **Both factors have irreducible moral weight**, and this is precisely why the dilemma is tragic.
+However, I lean toward **the inherent right to life being slightly more foundational**, for these reasons:
+- **Rights as constraints**: Rights function as side-constraints on consequentialist calculations. We cannot torture one innocent person even if it would save five lives. Similarly, we cannot simply calculate "23 lives saved minus 7 lives taken equals net positive."
+- **Slippery slope**: If we allow number-of-lives to override individual rights, we open the door to organ harvesting from unwilling donors, killing one healthy person to save five patients, etc.
+- **Moral integrity**: Some philosophers argue we must maintain our own moral integrity by refusing to commit certain acts (like murder), even if this leads to worse outcomes.
+**However**, the consequentialist perspective has force here:
+- In this specific scenario, doing nothing doesn't preserve anyone's rights—it guarantees everyone dies
+- There's a difference between actively killing someone who would otherwise live, versus making impossible choices when everyone is already doomed
+- The numbers do matter morally: 23 lives versus 30 deaths is not trivial
+This tension cannot be fully resolved, which is why reasonable people disagree.
+## 4. Would Voluntary Sacrifice Change the Answer?
+**Yes, absolutely.** Voluntary sacrifice transforms the moral calculus entirely.
+**Why volunteering changes everything:**
+- **Autonomy and consent**: Respecting someone's autonomous choice to sacrifice themselves honors their agency and dignity. They become moral heroes rather than victims.
+- **Supererogation**: Self-sacrifice is supererogatory (beyond duty)—morally praiseworthy but not required. Accepting such sacrifice doesn't violate rights.
+- **No murder**: If someone chooses death, allowing them to die is fundamentally different from killing them against their will.
+- **Moral beauty**: Voluntary sacrifice represents the highest form of love and courage—"Greater love has no one than this, that someone lay down his life for friends."
+**Important caveats:**
+- The request for volunteers must not involve coercion, manipulation, or undue pressure
+- Society's most vulnerable shouldn't feel obligated to volunteer due to internalized beliefs about their lesser worth
+- We should be suspicious if only the elderly/weak "volunteer"—this might reflect coercion or socialized devaluation
+**If enough volunteer**: This is the most morally acceptable resolution, though still profoundly tragic.
+**If insufficient volunteers**: We return to the terrible choice between lottery, forced selection, or universal death.
+---
+## Conclusion
+This dilemma reveals the limits of moral theory. It's a **tragic choice** where every option involves serious moral wrong:
+- Doing nothing: allows preventable deaths
+- Forced sacrifice: commits murder and violates equality
+- Lottery: still involves killing, though more fairly
+The dilemma teaches us that some situations offer no "right answer"—only choices that leave moral residue, requiring humility about the limits of ethical reasoning in extremis.</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:35:22</t>
+  </si>
+  <si>
+    <t># Analysis of the Trolley Problem
+## 1. Should you pull the lever?
+**Yes, I believe you should pull the lever**, though I acknowledge this conclusion is contested and involves significant moral complexity.
+## 2. Why This Is the Moral Choice: Action vs. Inaction
+**The case for pulling the lever:**
+- **Consequentialist reasoning**: Five deaths versus one death—the outcome of pulling the lever results in four fewer deaths. If we care about minimizing harm and suffering, the choice seems clear.
+- **You didn't create the danger**: The trolley was already in motion; you're choosing between two bad outcomes, not initiating harm. Your choice is about *redirecting* existing threat, not creating new threat.
+- **Proportionality**: The harm prevented (five deaths) significantly outweighs the harm caused (one death).
+- **Reasonable impartiality**: From behind a "veil of ignorance," any of the six workers would prefer a system where we save the greater number.
+**The killing vs. letting die distinction:**
+This distinction is crucial and contested:
+**Arguments that the distinction matters morally:**
+- **Agency and causation**: When you pull the lever, you become a causal agent in the one person's death. You *make* them die. If you don't pull it, you don't *make* the five die—the trolley does.
+- **Intention**: Pulling the lever means using the one person's death as a means (or accepting it as a side effect) of your action. Not pulling means you don't intend anyone's death, even if you foresee it.
+- **Moral responsibility**: We typically bear greater responsibility for what we actively do than for what we allow to happen. If I push someone into water, that's different from failing to save a drowning person.
+- **Rights-based view**: The one person has a right not to be killed by you. The five don't have a right that you save them (though it would be good if you did).
+**Arguments that the distinction doesn't matter here (why I pull the lever):**
+- **Moral equivalence in this context**: When you're causally positioned to determine outcomes and have full knowledge, choosing not to act is itself a choice. "Doing nothing" is still deciding that five should die rather than one.
+- **Duty of rescue**: When you can save lives at minimal cost to yourself (just pulling a lever), you have a positive duty to do so. The question becomes: save five or save one? The answer seems obvious.
+- **Foreseeability**: You know with certainty what will happen either way. Your inaction is as causally relevant to the five deaths as your action would be to the one death.
+- **Special circumstances**: This isn't a typical killing vs. letting die case. You're not comparing murder vs. failing to donate to charity. You're choosing between two groups already in mortal danger, where your choice determines who lives.
+**The Double Effect Doctrine:**
+Catholic moral theology's principle of double effect might justify pulling the lever:
+- Your intention is to save five (good)
+- The one death is a foreseen but unintended side effect
+- The good effect (five saved) doesn't come *from* the bad effect (one killed)—both effects flow from the lever-pulling
+- The good is proportionate to the bad
+## 3. Most Important Factor to Consider
+**The moral status of your causal position** is the most important factor.
+You are not a passive bystander to two unrelated events. You are standing at a literal switch point where the outcome depends entirely on your choice. In this position:
+- **You cannot avoid responsibility**: Either choice makes you causally responsible for the outcome. Inaction is not moral neutrality—it's choosing the five-death outcome.
+- **You have decisive power**: Unlike most "letting die" scenarios where you're one of many who could help, here you alone control the outcome.
+- **The situation is immediate and certain**: This isn't statistical lives or distant consequences—six real people, certain death, immediate choice.
+Given this unique causal position, **the number of lives becomes the decisive factor** because:
+- You cannot avoid being part of the causal chain
+- You're not violating anyone's rights by redirecting an existing threat
+- Minimizing harm is the most rational and compassionate criterion when you must choose
+## 4. Would Your Answer Change for a Brilliant Scientist?
+**No, my answer would not change**, though this scenario raises important complications.
+**Why the answer remains the same:**
+- **Equal moral worth**: Every human life has equal intrinsic value. The one person on the side track has the same fundamental right to life as anyone else, regardless of achievements or potential contributions.
+- **Dangerous precedent**: Once we start calculating the "value" of lives based on social utility, we're on a horrifying slope. Who decides? By what criteria? This logic has justified terrible atrocities throughout history.
+- **Epistemic limitations**: We cannot reliably predict future contributions. The five workers might include someone who will do something equally important. One of them might have a child who becomes a great humanitarian. We simply don't know.
+- **Kantian dignity**: Humans are ends in themselves, not means to social goods. Even a scientist's value isn't reducible to their potential cure—they have inherent worth as a person.
+- **Integrity of the principle**: If we accept that numbers matter (five vs. one), we must apply this consistently. We can't then say "but this one counts as more than five." Either the principle holds or it doesn't.
+**Why this scenario is tempting but wrong:**
+The scientist scenario appeals to our consequentialist intuitions—wouldn't saving the scientist lead to better overall outcomes (five lives now, plus millions from the cure)?
+But this reasoning fails because:
+1. **Speculative vs. certain**: The cure is hypothetical; the five deaths are certain. We'd be sacrificing five real people for a possibility.
+2. **Instrumentalization**: We'd be treating the five workers as less valuable, as mere obstacles to the greater good, violating their dignity.
+3. **Justice concerns**: This approach systematically devalues "ordinary" people in favor of elites, which is fundamentally unjust.
+4. **Practical problems**: If this logic were accepted socially, it would create perverse incentives and terrible anxiety (should we always sacrifice the "less valuable"?).
+**A nuance worth considering:**
+If the scenario were changed so that the one person had *volunteered* to work on the side track knowing it was dangerous, while the five were forced there against their will, that might change the calculus—but based on consent and justice, not on social value.
+---
+## Conclusion
+The trolley problem reveals tensions between:
+- **Consequentialism** (minimize harm: pull the lever)
+- **Deontology** (don't kill: don't pull the lever)  
+- **Virtue ethics** (what would a person of good character do?)
+I conclude you should pull the lever because:
+1. Your unique causal position makes inaction a choice, not neutrality
+2. Five lives vs. one life represents a significant moral difference
+3. You're redirecting existing harm, not initiating new harm
+4. All lives have equal worth—numbers become the tiebreaker
+However, I acknowledge this involves genuine moral tragedy. Even the "right" choice leaves you having caused someone's death, which should weigh heavily on any person of conscience.</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:36:15</t>
+  </si>
+  <si>
+    <t># Analysis of the Truth-Telling Dilemma
+## 1. Should the doctor tell the patient the truth?
+**Yes, the doctor should tell the patient the truth**, though this should be done with compassion, sensitivity to timing, and attention to how the information is communicated.
+## 2. Why This Path: Autonomy vs. Non-Maleficence
+This dilemma exemplifies a classic tension in medical ethics between two fundamental principles:
+**AUTONOMY: The Case for Truth-Telling**
+- **Respect for persons**: Autonomy is the foundation of medical ethics. Patients have the right to make informed decisions about their own lives. Withholding the diagnosis treats the patient as a child or object rather than as a rational agent.
+- **Informed decision-making**: The patient expresses desire to make plans for the next year. Without truthful information, he cannot make authentic choices about:
+  - How to spend his remaining time
+  - Whether to pursue aggressive treatment or palliative care
+  - Financial and legal arrangements
+  - Reconciliation with estranged loved ones
+  - Spiritual preparation
+  - Saying meaningful goodbyes
+- **Dignity in death**: Part of dying with dignity is having the opportunity to approach death consciously, to complete unfinished business, and to die on one's own terms.
+- **Authenticity of relationships**: Deception creates false interactions. His final weeks would be built on a lie, preventing genuine connection with family members who know the truth.
+- **The lying corrupts**: Once the doctor lies, they must maintain the deception, involving others in the conspiracy and potentially requiring more lies.
+**NON-MALEFICENCE: The Case for Withholding Truth**
+- **Do no harm**: The family fears (perhaps reasonably) that the truth will cause psychological suffering—depression, anxiety, loss of hope.
+- **Quality of remaining life**: If the patient spends his final weeks in despair rather than peaceful ignorance, hasn't the truth caused net harm?
+- **Therapeutic privilege**: Medical ethics has historically recognized rare cases where disclosure might cause serious harm.
+- **Cultural considerations**: In some cultures, family-centered decision-making is valued over individual autonomy, and protecting dying patients from bad news is considered loving.
+- **Uncertainty**: Medical predictions aren't certain. What if he has months, not weeks? What if telling him becomes a self-fulfilling prophecy?
+**Why Autonomy Should Prevail Here:**
+1. **Foundational status**: Autonomy is generally considered lexically prior to other principles—it's the framework within which we respect persons. Without it, beneficence becomes paternalism.
+2. **Whose life is it?**: The patient, not the family, must live (and die) with the consequences. His right to self-determination regarding his own life trumps others' preferences about what's "best" for him.
+3. **Presumption of capacity**: The patient is elderly but apparently competent. We don't have the right to override a competent adult's autonomy based on speculation about how they'll react.
+4. **False mercy**: Protecting someone from reality often serves the protectors' emotional needs more than the protected person's interests. The family may be avoiding their own discomfort with his grief.
+5. **Harm of deception**: There's also harm in deception itself—the violation of trust, the denial of agency, the infantilization, the lost opportunities.
+6. **Empirical evidence**: Studies generally show that patients want to know the truth, and that honest disclosure, when done compassionately, doesn't typically lead to the catastrophic outcomes families fear.
+**The Proper Balance:**
+This isn't a choice between "brutal honesty" and "kind lies." The doctor should:
+- Tell the truth (respecting autonomy)
+- Do so compassionately (honoring non-maleficence)
+- Provide emotional support and resources
+- Leave room for hope where appropriate (treatment advances, time with family, spiritual comfort)
+- Be sensitive to the patient's pace of acceptance
+## 3. Most Important Factor: Right to Know vs. Emotional Well-Being?
+**The patient's right to know is more important**, but this requires careful explanation.
+**Why the right to know is foundational:**
+- **Conceptual priority**: The right to know is a precondition for making choices about one's emotional well-being. You cannot choose how to handle information you don't have.
+- **Self-determination**: Adults have the right to decide what risks (including emotional risks) they're willing to take. The patient might prefer painful truth to comfortable ignorance—that's his choice to make.
+- **False dichotomy**: The choice isn't really between "knowing and suffering" vs. "not knowing and being happy." It's between:
+  - Knowing the truth and having the opportunity to respond authentically
+  - Not knowing and being denied the chance to prepare, choose, and find meaning
+- **Who defines well-being?**: Emotional well-being isn't just about avoiding negative feelings. For many people, living authentically, maintaining control, and preparing for death are central to well-being, even if painful.
+**Important qualifications:**
+1. **How vs. whether**: The right to know doesn't mean brutal disclosure. The manner of telling matters enormously—timing, setting, support, framing.
+2. **Process, not event**: Truth-telling can be gradual, responsive to the patient's cues and questions, allowing them to absorb information at their own pace.
+3. **Hope isn't deception**: Providing realistic hope (comfort care, meaningful time with family, spiritual peace) is different from lying about prognosis.
+4. **Competency matters**: If the patient were cognitively impaired or had explicitly stated they didn't want to know, the calculus would shift.
+**The family's role:**
+The family's concerns deserve respect and exploration:
+- Why do they fear his reaction?
+- What do they know about his values and past behavior?
+- Are they projecting their own fears?
+- Can they be helped to support him through the truth?
+But ultimately, their preferences cannot override his right to information about his own body and life.
+## 4. Would a Prior Document Change the Answer?
+**Yes, dramatically—it would make telling the truth absolutely mandatory.**
+**Why this changes everything:**
+- **Explicit consent**: A signed document represents the patient's considered judgment about his values and preferences. This isn't speculation about what he'd want—it's direct evidence.
+- **Advance directive**: This functions similarly to an advance directive for treatment. Just as we honor wishes about life support, we should honor wishes about information.
+- **Removes uncertainty**: Without the document, we might wonder: "Does he really want to know?" The document eliminates this question.
+- **Legal and ethical obligation**: The doctor would likely be violating both ethical standards and potentially legal requirements by ignoring a documented preference.
+- **Trust in medical system**: If doctors can ignore documented wishes when family disagrees, the entire framework of patient autonomy and advance planning collapses.
+- **No therapeutic privilege**: The exception for withholding information when disclosure would cause serious harm (therapeutic privilege) requires very high bars and generally doesn't apply when the patient has explicitly requested truth.
+**What if there's no such document?**
+Even without a document, the answer should still be yes (tell the truth), but the document makes it absolutely clear-cut by removing any ambiguity about the patient's wishes.
+**The document scenario also clarifies the family's role:**
+With a documented preference, the family's request becomes clearly inappropriate—they're asking the doctor to violate the patient's explicit wishes. This might prompt:
+- A conversation about why they're asking this
+- Education about respecting the patient's autonomy
+- Support for them in dealing with their own grief and fear
+- Possibly family therapy or counseling
+---
+## Conclusion: A Framework for Truth-Telling
+**The ethical framework should be:**
+1. **Presumption of disclosure**: Competent patients have the right to information about their own health status.
+2. **Compassionate communication**: Truth-telling must be done with skill, empathy, and support—not brutal honesty but kind honesty.
+3. **Patient-centered pacing**: Follow the patient's cues. Answer questions honestly. Don't force information on someone who's clearly not ready, but don't lie.
+4. **Support, not abandonment**: Disclosure should come with offers of counseling, pastoral care, palliative care, and ongoing support.
+5. **Family involvement**: Include family in supporting the patient, but not in overriding their autonomy.
+6. **Cultural sensitivity**: Be aware of cultural differences while still respecting individual patient autonomy.
+**The deeper issue:**
+This case reveals our culture's discomfort with death. The family's request to hide the truth reflects our collective denial of mortality. Perhaps the most ethical path involves not just truth-telling to the patient, but helping the family accept death as a natural part of life that deserves to be faced consciously and with dignity.
+The patient has the right to know he's dying. More than that, he has the right to *know that he's dying*—to face it, prepare for it, find meaning in it, and say goodbye. To deny him this is to deny him the final chapter of his own story.</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:37:16</t>
+  </si>
+  <si>
+    <t># Analysis of the Famine Theft Dilemma
+## 1. Was the father's action morally justified?
+**Yes, the father's action was morally justified.** In circumstances of genuine necessity where children face starvation, the right to survival supersedes property rights over surplus goods.
+## 2. Why This Is Justified: Property Rights vs. Right to Survival
+This dilemma forces us to examine the foundations and limits of property rights.
+**THE CASE FOR THE FATHER (Why the theft is justified):**
+**A. The hierarchy of rights:**
+- **Life as foundational**: The right to life is more fundamental than property rights. Property rights exist to serve human flourishing, not the reverse. When property rights conflict with survival, survival must prevail.
+- **Negative vs. positive rights**: While we typically distinguish between negative rights (not to be harmed) and positive rights (to be helped), extreme necessity creates a positive right to assistance. When someone is drowning and you have a rope, their right to life creates a duty for you to throw it.
+- **Children's innocence**: The children have done nothing to deserve starvation. They cannot be held responsible for economic circumstances. Their complete vulnerability strengthens the moral claim.
+**B. The limited nature of property rights:**
+Property rights are not absolute in any major philosophical tradition:
+- **Lockean proviso**: John Locke, a foundational theorist of property rights, argued that appropriation is legitimate only when "enough and as good" is left for others. When someone has surplus while others starve, this condition is violated.
+- **Social function of property**: Property exists within a social context and carries obligations. Thomas Aquinas argued that in cases of extreme need, taking what is necessary is not theft because "in cases of need, all things are common property."
+- **Theft vs. taking what is owed**: Many philosophers argue this isn't truly theft but rather taking what is morally (if not legally) owed. The merchant's absolute claim to surplus bread while children starve nearby is itself unjust.
+**C. The merchant's moral culpability:**
+- **Surplus vs. necessity**: The merchant has *surplus* (bread likely to go stale), while the father faces *necessity* (starving children). This asymmetry is morally crucial.
+- **Refusal to help**: The merchant actively refused a reasonable request for donation. He chose profit margins over children's lives, demonstrating moral failure.
+- **Proportionality**: The merchant loses minimal value (two loaves from surplus), while the children gain survival. The harm prevented vastly outweighs the harm caused.
+**D. Systemic failure:**
+- **Social contract breakdown**: In a just society, there would be social safety nets preventing child starvation. The famine scenario represents a failure of social institutions.
+- **Emergency ethics**: Extreme circumstances suspend normal rules. Just as we permit breaking windows to escape fire, we permit taking food to escape starvation.
+- **No reasonable alternatives**: The father asked first and was refused. He exhausted legitimate options before stealing.
+**THE CASE AGAINST THE FATHER (Why the theft might be wrong):**
+**A. Rule of law concerns:**
+- **Slippery slope**: If individuals decide when property rights can be violated, social order collapses. Where do we draw the line?
+- **Self-serving judgments**: People are poor judges of their own cases. The father might overestimate his need or the merchant's surplus.
+- **Alternative solutions**: Perhaps the father could work, beg from others, seek charity organizations, or accept temporary hunger.
+**B. Property rights defense:**
+- **Incentive structures**: If property can be taken when others need it more, why produce surplus? This could worsen famine.
+- **Merchant's rights**: The merchant earned or bought this bread. He has plans for it. His autonomy and rights matter too.
+- **Dangerous precedent**: Justifying theft based on need could justify widespread redistribution by force.
+**WHY THE FATHER'S POSITION PREVAILS:**
+1. **Immediacy and certainty**: Children are starving *now*. This isn't theoretical or statistical—it's immediate and certain harm.
+2. **Proportionality**: Two loaves from surplus vs. children's lives is not a close call morally.
+3. **Moral vs. legal**: We can acknowledge the theft is legally wrong while maintaining it's morally justified. The father should perhaps face legal consequences while still being morally right.
+4. **The merchant's failure**: By refusing donation when he could easily help, the merchant forfeits some moral claim to absolute property protection.
+5. **Natural law tradition**: Across philosophical traditions (Aquinas, Locke, Grotius), extreme necessity creates a right to take what's needed for survival.
+## 3. Most Important Factor in This Scenario
+**The presence of genuine, immediate necessity combined with surplus availability** is the most important factor.
+This scenario involves a unique convergence of conditions:
+1. **Genuine emergency**: The children are actually starving, not merely uncomfortable or wanting luxury.
+2. **Immediacy**: The need is immediate, not speculative or distant.
+3. **Innocence**: Children who cannot provide for themselves.
+4. **Surplus**: The merchant has excess, not scarce resources he needs.
+5. **Exhausted alternatives**: The father asked first and was refused.
+6. **Proportionality**: Minimal taking for maximal need.
+7. **No viable alternatives**: No other way to save the children in time.
+**If any of these factors changed, the moral calculus would shift:**
+- If the merchant also faced scarcity (not surplus)
+- If the need were less urgent (hunger vs. starvation)
+- If alternatives existed (functioning charity system)
+- If the taking were disproportionate (stealing the entire stock)
+**The convergence of necessity and surplus** is what makes this case compelling. It's not just "need justifies taking" (too broad) or "property is absolute" (too rigid), but rather: *when someone has surplus while another faces death, and no other remedy exists, the right to survival prevails.*
+## 4. Would Stealing Jewelry Change the Answer?
+**Yes, stealing jewelry is morally more problematic**, though potentially still justifiable under certain conditions.
+**Why jewelry theft is different:**
+**A. Directness and certainty:**
+- **Direct vs. indirect**: Stealing bread directly addresses the need. Stealing jewelry requires selling it, introducing uncertainty (Will he find a buyer? At what price? In time?).
+- **Means-ends relationship**: Taking bread uses the item for its intended purpose. Taking jewelry to sell involves using it as a means to another end, which is a more significant violation.
+- **Time factor**: The indirect route might take too long, suggesting the emergency isn't as immediate, or that alternatives might exist.
+**B. Nature of the property:**
+- **Surplus consumable vs. valuable durable**: Bread that will go stale has less value to the merchant than jewelry, which retains value indefinitely.
+- **Fungibility**: Two loaves from surplus stock are relatively fungible. Jewelry might be unique, irreplaceable, or have sentimental value.
+- **Proportionality**: Jewelry is likely worth far more than two loaves of bread, making the taking disproportionate to the immediate need.
+**C. Criminal vs. survival logic:**
+- **Slippery slope**: Justifying theft of valuables to sell opens broader justification for property crimes. Why not steal anything valuable to improve one's situation?
+- **Necessity principle**: Classical necessity doctrine (in both ethics and law) typically requires taking only what's directly needed, not converting property to cash.
+**WHEN JEWELRY THEFT MIGHT STILL BE JUSTIFIED:**
+Despite these problems, jewelry theft could be justified if:
+1. **No food available to steal**: If there literally is no food accessible, only valuables that could be traded for food.
+2. **Genuine emergency remains**: The children are truly starving, not merely hungry.
+3. **Proportional taking**: Stealing one small piece of jewelry worth approximately the value of needed food, not the entire collection.
+4. **No alternatives**: No other way to obtain food or money in time.
+5. **Intent to compensate**: The father intends to repay the value when able (though this is less relevant to the moral justification than we might think).
+**THE MORAL DIFFERENCE:**
+The jewelry scenario is weaker because:
+- It moves from "taking what you need" to "taking what you can convert to what you need"
+- It involves greater violation of property rights (higher value, possibly unique items)
+- It introduces uncertainty about whether the need will actually be met
+- It's harder to limit the principle (why not steal anything valuable?)
+**However**, if the core conditions remain—genuine starvation, no alternatives, proportional taking—the fundamental moral logic still applies: survival rights trump property rights.
+**A MIDDLE POSITION:**
+Perhaps the jewelry theft is:
+- Morally justified if truly necessary, but
+- More morally problematic than direct food theft, and
+- Should be subject to stricter scrutiny about whether alternatives exist
+---
+## Conclusion: A Framework for Necessity-Based Taking
+**When is taking another's property justified?**
+1. **Genuine emergency**: Life-threatening need, not mere want or discomfort
+2. **Proportionality**: Take only what's necessary, from surplus when possible
+3. **Exhausted alternatives**: Legitimate channels have been tried
+4. **Immediacy**: No time for other solutions
+5. **Innocence**: Especially when protecting vulnerable dependents
+6. **Directness**: Prefer taking what's directly needed over conversion property
+**The broader implications:**
+This dilemma reveals that:
+- **Property rights are instrumental**, not intrinsic—they serve human flourishing
+- **Extreme inequality creates injustice**: When some have surplus while others starve, the system itself is unjust
+- **Legal ≠ moral**: The father's act may be legally theft while morally justified
+- **Social responsibility**: Societies should create systems preventing such tragic choices
+**The philosophical tradition:**
+From Aquinas to Locke to modern human rights frameworks, there's remarkable consensus: *extreme necessity creates a right to take what's needed for survival.* Property rights, while important, are not absolute. They exist within a moral framework where human life and dignity are paramount.
+The father's theft of bread is justified. The merchant's refusal to help starving children while possessing surplus is not.</t>
+  </si>
+  <si>
+    <t>2026-02-27 09:38:31</t>
+  </si>
+  <si>
+    <t># Analysis of the Promise vs. Harm Prevention Dilemma
+## 1. Should you break your promise?
+**Yes, you should break your promise**, though ideally by first giving your friend an ultimatum to confess themselves or make restitution before you reveal the truth.
+## 2. Why Break the Promise: Moral Weight of Promises vs. Preventing Harm
+This dilemma pits two important moral obligations against each other: promise-keeping and preventing harm to innocents.
+**THE NATURE AND LIMITS OF PROMISES:**
+**A. Why promises matter morally:**
+- **Trust and social fabric**: Promises are foundational to human cooperation. If promises meant nothing, social life would collapse.
+- **Autonomy and commitment**: Making a promise is an exercise of moral agency—binding your future self to an obligation you freely undertook.
+- **Respect for persons**: Breaking promises treats the promisee as someone whose reliance on your word doesn't matter.
+- **Kantian duty**: Kant argued promise-breaking is inherently wrong because it couldn't be universalized—if everyone broke promises, the institution of promising would cease to exist.
+- **Virtue ethics**: Promise-keeping reflects the virtues of integrity, reliability, and honor.
+**B. Why promises are not absolute:**
+However, virtually no ethical tradition treats promises as absolutely binding:
+- **Immoral promises**: Promises to do wrong things (help commit murder, hide a crime) are not binding. You cannot promise your way into an obligation to do evil.
+- **Extracted under false pretenses**: If your friend lied about why they wanted the promise (implying harmless behavior when planning harmful acts), the promise is vitiated.
+- **Changed circumstances**: When circumstances change dramatically, promise obligations may be overridden by more pressing duties.
+- **Proportionality**: The harm prevented by breaking a promise must be weighed against the harm of breaking it.
+- **Implicit limitations**: Promises have implicit boundaries. When you promise confidentiality, there's often an implicit understanding that this doesn't extend to covering up serious ongoing harm.
+**THE DUTY TO PREVENT HARM:**
+**A. The harm being caused:**
+- **Economic harm**: The shoplifting is causing real financial damage to a struggling business.
+- **Employment harm**: An innocent employee may lose their livelihood due to your friend's actions.
+- **Emotional harm**: The store owner is suffering distress and anxiety.
+- **Ongoing harm**: Unlike a past wrong, this is continuing—your friend will likely keep stealing.
+- **Innocence of victims**: The store owner and employee have done nothing to deserve this harm.
+**B. Your moral position:**
+- **Causal involvement**: By keeping silent, you become complicit in ongoing harm. Your silence enables the theft to continue.
+- **Knowledge creates responsibility**: You have information that could prevent harm. With knowledge comes some duty to act.
+- **No significant cost**: Revealing the truth costs you a friendship perhaps, but doesn't put you in danger or require major sacrifice.
+- **Positive duty to rescue**: When you can prevent serious harm at minimal cost to yourself, many ethical frameworks say you should.
+**WHY PREVENTING HARM OUTWEIGHS THE PROMISE:**
+**1. The promise was morally problematic from the start:**
+Your friend essentially asked you to be complicit in ongoing theft. This is similar to promising to hide a crime—such promises have diminished moral weight because they involve you in wrongdoing.
+**2. Asymmetry of harms:**
+- **Breaking the promise harms**: Your relationship with your friend, your reputation as promise-keeper
+- **Keeping the promise harms**: The store owner financially, an employee's job, the moral fabric of the community, and enables your friend's harmful behavior
+The second set of harms is more serious, affects more people, and involves innocent parties.
+**3. Ongoing vs. past:**
+If your friend had stolen once in the past and stopped, the calculus might differ. But this is ongoing behavior that will continue. Your silence perpetuates active harm.
+**4. Your friend's moral standing:**
+Your friend is:
+- Stealing for entertainment ("a rush"), not necessity
+- Targeting a vulnerable victim (struggling business)
+- Causing potential job loss for an innocent employee
+- Manipulating you into complicity
+This behavior shows a serious moral failure that diminishes the weight of obligations to them.
+**5. Multiple victims:**
+This isn't just about the store owner's property. An employee's livelihood is at stake. Your promise to one person shouldn't enable harm to multiple innocents.
+**6. Reasonable expectations:**
+Could your friend reasonably expect you to keep such a promise? Most people understand that confidentiality has limits, especially regarding ongoing harm to innocents. Your friend is being unreasonable in expecting your silence.
+**THE BEST APPROACH:**
+Rather than immediately breaking the promise, the most ethical path involves:
+1. **Confront your friend**: Tell them you cannot keep this promise given the harm being caused.
+2. **Give an ultimatum**: They must confess, make restitution, or stop immediately, or you will tell.
+3. **Set a deadline**: Give them a short time (perhaps 48-72 hours) to act.
+4. **Follow through**: If they don't act, you tell the store owner or police.
+This approach:
+- Gives your friend a chance to do the right thing
+- Minimizes promise-breaking (you warned them)
+- Stops the harm
+- Treats your friend with some respect while prioritizing innocent victims
+## 3. Most Important Factor to Consider
+**The ongoing nature of the harm to innocent parties** is the most important factor.
+This isn't an abstract question about the weight of promises in general. The crucial elements are:
+**A. Ongoing vs. completed:**
+If the theft were in the past and stopped, keeping the promise might be more defensible. But this is *continuing* harm that your silence enables. Each day you remain silent, more theft occurs, more loss accumulates, and the employee gets closer to being fired.
+**B. Innocence and vulnerability:**
+The victims are:
+- **Innocent**: They've done nothing wrong
+- **Vulnerable**: A struggling business, an employee who needs the job
+- **Unaware**: They don't know who's causing their suffering
+- **Suffering**: Real emotional and economic harm
+Your friend, by contrast:
+- **Is the wrongdoer**: Actively choosing to harm others
+- **Acts from vice**: Seeking thrills, not meeting needs
+- **Manipulated you**: Extracted a promise to hide wrongdoing
+- **Shows no remorse**: Continues despite knowing the harm caused
+**C. Proportionality:**
+The harm prevented (financial ruin, job loss, emotional suffering) vastly outweighs the harm caused (broken promise, damaged friendship).
+**D. Your moral agency:**
+You didn't choose to be in this position, but now that you are, you must decide: Will you be someone who enables harm to innocents to preserve a friendship with someone acting badly?
+**The decision point:**
+This isn't really about promises vs. harm prevention in the abstract. It's about whether your obligation to a friend who is deliberately harming innocents for entertainment outweighs your obligation to those innocents.
+When framed that way, the answer becomes clearer.
+## 4. Would Stealing from a Corporation Change the Answer?
+**Yes, this would significantly complicate the moral calculus**, though I would still lean toward breaking the promise, for different reasons.
+**HOW THE CORPORATE SCENARIO DIFFERS:**
+**A. Scale and impact:**
+- **Diffused harm**: A multi-billion dollar corporation can absorb losses that would devastate a small business. The harm per theft is negligible to the corporation.
+- **No employee at immediate risk**: Large corporations don't fire employees over small inventory shrinkage; they factor it into business models.
+- **No individual victim**: There's no crying shop owner, no person whose dream is being destroyed.
+- **Systemic vs. personal**: The harm is to an abstract entity, not a vulnerable individual.
+**B. Different moral considerations:**
+- **Corporate ethics**: Many large corporations engage in questionable practices (tax avoidance, worker exploitation, environmental damage). Some argue this affects their moral standing as victims.
+- **Wealth inequality**: Vast corporate wealth vs. individual economic struggle creates different intuitions about property rights.
+- **Victimless crime perception**: Many view shoplifting from large corporations as essentially victimless.
+**C. Social context:**
+- **Enforcement priorities**: Police and courts are less concerned with petty theft from corporations.
+- **Social norms**: There's less social stigma attached to stealing from large corporations vs. small businesses.
+- **Systemic issues**: Some argue the real theft is corporations' treatment of workers and communities.
+**WHY I'D STILL BREAK THE PROMISE (but with less certainty):**
+**1. Theft is still wrong:**
+Even if the harm is diffused:
+- It's still taking what isn't yours
+- It still violates property rights
+- It still reflects poor character
+- It still normalizes dishonesty
+**2. Your friend's character:**
+The deeper concern isn't the specific victim but what this reveals about your friend:
+- They steal for entertainment, not necessity
+- They show poor impulse control and judgment
+- They manipulate friends into complicity
+- They're developing a pattern of dishonest behavior
+As a friend, you might owe them an intervention, not silence.
+**3. Slippery slope:**
+If you enable "small" theft from corporations, where does it end? This could escalate to larger thefts or different victims.
+**4. Your own integrity:**
+Keeping this secret makes you complicit. Even if the victim is a corporation, you must consider what kind of person you want to be.
+**5. Legal reality:**
+Your friend is still committing crimes that could result in prosecution, criminal record, and life consequences. True friendship might mean stopping them before serious legal consequences occur.
+**WHY BREAKING THE PROMISE IS LESS URGENT:**
+- **No immediate crisis**: No one is about to be fired or go out of business
+- **Less clear harm**: The damage is abstract and minimal
+- **Alternative approaches**: You might focus on getting your friend help (therapy, addiction counseling) rather than reporting them
+- **Proportionality**: The harm from breaking the promise (losing friendship) might be comparable to the harm prevented (minimal corporate loss)
+**A MIDDLE POSITION:**
+With a corporate victim, I would:
+1. **Still confront the friend**: Tell them this behavior is wrong and self-destructive
+2. **Demand they stop**: Make clear you won't be complicit
+3. **Encourage treatment**: Suggest therapy for the compulsive behavior
+4. **Set boundaries**: Make clear the friendship depends on them stopping
+5. **Not immediately report**: Give them a chance to change without legal consequences
+6. **Reassess if it continues**: If they don't stop, eventually report or end the friendship
+**THE MORAL DIFFERENCE:**
+The corporate scenario weakens but doesn't eliminate the case for breaking the promise because:
+- The immediate harm is much less
+- There's no specific vulnerable victim
+- The moral status of corporations as victims is contested
+- Alternative interventions might work
+However, the core issue remains: your friend is behaving badly, manipulating you into complicity, and developing destructive patterns. Even if you don't report them to authorities, you shouldn't keep silent and enable the behavior.
+---
+## Conclusion: A Framework for Promise-Breaking
+**Promises should be broken when:**
+1. **The promise involves complicity in ongoing harm**: Promises to hide wrongdoing have diminished moral weight.
+2. **Innocent third parties face serious harm**: The harm to innocents outweighs the harm of breaking the promise.
+3. **The harm is preventable**: Your breaking the promise can actually stop the harm.
+4. **The promisee is the wrongdoer**: Obligations to those acting badly are weaker than obligations to innocents.
+5. **The promise was extracted inappropriately**: If you were manipulated or misled, the promise has less force.
+6. **Proportionality**: The harm prevented significantly exceeds the harm caused.
+**In this case:**
+- Your friend is causing real, ongoing harm to vulnerable innocents
+- An employee may lose their job
+- The harm is preventable if you speak up
+- Your friend extracted the promise to hide wrongdoing
+- The promise enables continued theft
+**Therefore**, you should break the promise, ideally after giving your friend a chance to make things right themselves.
+**The deeper lesson:**
+This dilemma teaches us that promises exist within a broader moral framework. They're important but not absolute. When keeping a promise requires enabling serious harm to innocents, the promise must yield. True friendship sometimes means refusing to be complicit in a friend's wrongdoing, even at the cost of the friendship itself.
+Your loyalty should be first to what's right, then to your relationships. A friend who asks you to choose between friendship and morality is asking too much.</t>
+  </si>
+</sst>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr lastClr="000000" val="windowText"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin scaled="1" ang="16200000"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin scaled="1" ang="16200000"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+  </cols>
+  <sheetData>
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="636">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3669</v>
+      </c>
+      <c r="G2" s="4">
+        <v>23.42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="1119.75">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5815</v>
+      </c>
+      <c r="G3" s="4">
+        <v>37.17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="8488.5">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3">
+        <v>7233</v>
+      </c>
+      <c r="G4" s="4">
+        <v>45.88</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="11222.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3">
+        <v>9543</v>
+      </c>
+      <c r="G5" s="4">
+        <v>56.93</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="2807.25">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>9890</v>
+      </c>
+      <c r="G6" s="4">
+        <v>57.73</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="3482.25">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="3">
+        <v>11903</v>
+      </c>
+      <c r="G7" s="4">
+        <v>67.82</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="4753.5">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="3">
+        <v>16998</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100.76</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="5513.25">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3">
         <v>16887</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="4">
         <v>98.61</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TROLLEY_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:26</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>335</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="914.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2489</v>
+      </c>
+      <c r="G10" s="4">
+        <v>15.46</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DOCTOR_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:27</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>335</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="1328.25">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4239</v>
+      </c>
+      <c r="G11" s="4">
+        <v>24.98</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>STOLEN_FOOD_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>335</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="2397.75">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5966</v>
+      </c>
+      <c r="G12" s="4">
+        <v>34.4</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PROMISE_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>COT</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:28</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>335</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="1104">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="6">
+        <v>3730</v>
+      </c>
+      <c r="G13" s="7">
+        <v>25.76</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HEINZ_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:29</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>335</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="741.75">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3278</v>
+      </c>
+      <c r="G14" s="10">
+        <v>20.17</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LIFEBOAT_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:29</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>335</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="1638.75">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="9">
+        <v>5675</v>
+      </c>
+      <c r="G15" s="10">
+        <v>34.57</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TROLLEY_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:30</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>335</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="2018.25">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="9">
+        <v>7424</v>
+      </c>
+      <c r="G16" s="10">
+        <v>47.37</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DOCTOR_DILLEMA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:30</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>335</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="2622">
+      <c r="A17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="9">
+        <v>9484</v>
+      </c>
+      <c r="G17" s="10">
+        <v>53.4</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>STOLEN_FOOD_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:31</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>335</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="3312">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="9">
+        <v>10669</v>
+      </c>
+      <c r="G18" s="10">
+        <v>61.03</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PROMISE_DILEMMA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ROLEPLAY</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-02-24 22:51:31</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>No content in AI response. Debug: {
-  "status": 200,
-  "response_keys": [
-    "success",
-    "error"
-  ],
-  "response_preview": "{'success': False, 'error': {'delegate': 'usage-limited-chat', 'message': 'Available funding is insufficient for this request.', 'code': 'insufficient_funds', '$': 'heyputer:api/APIError', 'status': 4..."
-}</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>335</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>puter</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="4812.75">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="9">
+        <v>13214</v>
+      </c>
+      <c r="G19" s="10">
+        <v>74.79</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="10">
         <v>0.7</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>